--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="RoguelikeCards" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="📖 옵션_도움말_가이드" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +36,37 @@
       <name val="Malgun Gothic"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -45,8 +75,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002A364F"/>
-        <bgColor rgb="002A364F"/>
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00334155"/>
+        <bgColor rgb="00334155"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00475569"/>
+        <bgColor rgb="00475569"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -86,6 +134,32 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -161,6 +235,117 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>DPS: Fire Mage 엔진</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>카드의 고유 시스템 ID입니다. 영문 소문자와 밑줄로 작성합니다.
+(예: rapid_haste_1)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>게임 내 카드 상단에 표시될 한글 이름입니다.
+(예: 화염의 손길)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>카드 대표 이모지 또는 아이콘 문자입니다.
+(예: ⚡, ☄️, 🔥, 🦅, 📖)</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>희귀도 등급 (드롭다운 제공):
+- common: 일반 (회색)
+- rare: 희귀 (하늘색)
+- epic: 영웅 (보라색)
+- legendary: 전설 (황금색, 보스전 우대)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>카드의 빌드 분류 태그 (드롭다운 제공):
+- rapid: 속사/가속 머신건
+- crit: 극치명타 몰열 누킹
+- pet: 불사조 정령 군단
+- util: 생존/골드 유틸
+- spell: 고대 주문서 해금</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>한 런(Run)에서 최대로 습득 가능한 횟수입니다.
+이 횟수만큼 습득하면 이후 3지선다 추첨 풀에서 자동 제외됩니다. (보통 1~5)</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>게임 내 카드 본문에 표시될 효과 설명문입니다.
+강조할 수치는 &lt;b&gt;+25%&lt;/b&gt; 태그로 감싸면 굵게 표시됩니다.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>습득 시 플레이어의 주문력(Spell Power)에 영구 가산됩니다.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>습득 시 플레이어의 가속도(% 단위)에 가산되어 시전 및 글쿨이 빨라집니다.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>습득 시 플레이어의 치명타율(% 단위)에 가산됩니다.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>습득 시 치명타 피해 배율(% 단위)에 가산됩니다.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>습득 시 몬스터 처치 골드 획득 배율(% 단위)에 가산됩니다.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>3지선다에 등장하기 위한 선행 조건 (드롭다운 제공):
+- has_summon: 소환수 보유 시에만 등장
+- has_meteor: 메테오 습득 시에만 등장
+- has_combustion: 발화 습득 시에만 등장
+- (빈칸): 조건 없이 항상 등장</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>고대 주문서 카드 습득 시 액션바에 해금할 스킬 키 (드롭다운 제공):
+- fireblast, meteor, combustion, summon, ice_barrier</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>시스템에 내장된 특수 고유 로직 키입니다.
+자세한 키 목록과 기능은 하단의 [📖 옵션_도움말_가이드] 시트를 참고하세요.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>특수 기믹에 전달할 세부 JSON 수치입니다.
+(예: {"executionerMult": 0.7})</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -458,22 +643,22 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -555,7 +740,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>rapid_spark</t>
@@ -601,7 +786,7 @@
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="22" customHeight="1">
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>rapid_power</t>
@@ -647,7 +832,7 @@
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>rapid_split</t>
@@ -695,7 +880,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>rapid_overdrive</t>
@@ -743,7 +928,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>rapid_gatling</t>
@@ -791,7 +976,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="22" customHeight="1">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>crit_focus</t>
@@ -837,7 +1022,7 @@
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>crit_multiplier</t>
@@ -883,7 +1068,7 @@
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>crit_chain_streak</t>
@@ -935,7 +1120,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>crit_meteor_storm</t>
@@ -987,7 +1172,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>crit_crimson_frenzy</t>
@@ -1039,7 +1224,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr"/>
     </row>
-    <row r="12" ht="22" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>sum_spirit</t>
@@ -1087,7 +1272,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="22" customHeight="1">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>sum_haste</t>
@@ -1143,7 +1328,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>sum_volley</t>
@@ -1195,7 +1380,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>sum_cinder_lord</t>
@@ -1247,7 +1432,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>util_gold_greed</t>
@@ -1291,7 +1476,7 @@
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>util_executioner</t>
@@ -1343,7 +1528,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>util_phoenix_reborn</t>
@@ -1391,7 +1576,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>spell_autocast</t>
@@ -1439,7 +1624,7 @@
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
     </row>
-    <row r="20" ht="22" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>spell_fireblast</t>
@@ -1487,7 +1672,7 @@
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
     </row>
-    <row r="21" ht="22" customHeight="1">
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>spell_meteor</t>
@@ -1535,7 +1720,7 @@
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
     </row>
-    <row r="22" ht="22" customHeight="1">
+    <row r="22" ht="24" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>spell_flame_patch</t>
@@ -1583,7 +1768,7 @@
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
+    <row r="23" ht="24" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>spell_combustion</t>
@@ -1633,22 +1818,1064 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="D2:D73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 희귀도" error="희귀도는 common, rare, epic, legendary 중에서 선택해주세요." type="list">
+    <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 희귀도" error="희귀도는 common, rare, epic, legendary 중에서 선택해주세요." promptTitle="[희귀도(rarity) 옵션 안내]" prompt="• common: 일반 (회색 테두리)&#10;• rare: 희귀 (파란색 테두리)&#10;• epic: 영웅 (보라색 테두리)&#10;• legendary: 전설 (황금 테두리, 보스전 우대)" type="list">
       <formula1>"common,rare,epic,legendary"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 빌드" error="빌드는 rapid, crit, pet, util, spell 중에서 선택해주세요." type="list">
+    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 빌드" error="빌드는 rapid, crit, pet, util, spell 중에서 선택해주세요." promptTitle="[빌드(build) 분류 안내]" prompt="• rapid: 속사/가속 화염구 난사&#10;• crit: 극치명타 몰열 메테오 누킹&#10;• pet: 불사조 정령 군단&#10;• util: 생존력 및 골드 유틸&#10;• spell: 고대 주문서 스킬 해금" type="list">
       <formula1>"rapid,crit,pet,util,spell"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 선행조건" error="선행조건 목록에서 선택하거나 빈칸으로 두세요." type="list">
+    <dataValidation sqref="M2:M100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 선행조건" error="선행조건 목록에서 선택하거나 빈칸으로 두세요." promptTitle="[선행조건(prerequisite) 안내]" prompt="해당 조건이 달성되어야만 3지선다에 등장합니다:&#10;• has_summon: 소환수 보유 시&#10;• has_meteor: 메테오 습득 시&#10;• has_combustion: 발화 습득 시&#10;• (빈칸): 조건 없이 항상 등장" type="list">
       <formula1>"has_summon,has_meteor,has_combustion,has_fireblast,has_ice_barrier"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 스킬 키" error="해금스킬 키 목록에서 선택하거나 빈칸으로 두세요." type="list">
-      <formula1>"fireblast,meteor,combustion,summon,ice_barrier"</formula1>
+    <dataValidation sqref="N2:N100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 스킬 키" error="해금스킬 키 목록에서 선택하거나 빈칸으로 두세요." promptTitle="[해금스킬(spellKey) 안내]" prompt="주문서 카드 습득 시 액션바에 해금할 스킬:&#10;• fireblast: 불꽃 작렬&#10;• meteor: 유성낙하&#10;• combustion: 발화&#10;• summon: 불사조 소환&#10;• ice_barrier: 얼음 보호막&#10;• autocast: 자동 시전 마법진" type="list">
+      <formula1>"fireblast,meteor,combustion,summon,ice_barrier,autocast"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 기믹 키" error="특수기믹 키 목록에서 선택하거나 빈칸으로 두세요." type="list">
-      <formula1>"scorch_multiplier,ignite_spread,phoenix_flame,phoenix_feather_boost,pyro_echo,mana_surge,alchemy_gold"</formula1>
+    <dataValidation sqref="O2:O100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 기믹 키" error="특수기믹 키 목록에서 선택하거나 빈칸으로 두세요." promptTitle="[특수기믹(mechanic) 안내]" prompt="시스템 특수 로직 키입니다.&#10;자세한 효과와 설정값은 하단의 [📖 옵션_도움말_가이드] 탭을 확인하세요!" type="list">
+      <formula1>"split_fireball,haste_stack,gatling_mode,chain_hot_streak,meteor_buff,combustion_god,extra_spirit,spirit_frenzy,synchronized_fire,cinder_lord,executioner,phoenix_reset"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>📚 DPS: Fire Mage 마도서 각성 파워업 카드 기획 가이드북</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>1. 희귀도 등급 (rarity) 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>카드의 희귀도는 카드 테두리 색상 및 추첨 확률(가중치)을 결정합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>값 (Enum)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>한글 명칭</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>시각 효과 / 테두리</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>게임 내 등장 규칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>회색/슬레이트 테두리</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>기본 등장 확률이 가장 높으며 주로 기본 스탯 강화 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>하늘색 테두리</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>중간 확률로 등장하며 빌드의 핵심 시너지 카드 구성</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>보라색 테두리</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>낮은 확률로 등장하며 빌드를 완성하는 강력한 위력 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>황금빛 테두리</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>매우 희귀하게 등장하며 보스 웨이브 클리어 시 우대 확률 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2. 빌드 성향 (build) 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>카드가 어떤 전투 플레이스타일을 지향하는지 분류하는 태그입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>값 (Enum)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>한글 명칭</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>주요 컨셉</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>핵심 메커니즘</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>rapid</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>속사 머신건</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>화염구 난사 및 극한의 가속도</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>시전 속도 단축, 화염구 분열, 게틀링 연속 발사</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>crit</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>극치명타 몰열</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>몰아치는 열기 누킹 및 메테오</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>확정 치명타 연계, 노코스트 메테오 투하, 발화 피버</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>pet</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>정령 군단</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>불사조 소환수 소환 및 군단 지휘</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>소환수 추가 소환, 소환수 공격 속도/피해량 증폭, 일제 사격</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>유틸리티</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>생존 및 경제적 보상 극대화</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>처형인 추가 피해, 골드 획득량 대폭 증가, 쿨다운 초기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>spell</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>고대 주문서</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>새로운 마법 스킬 습득</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>액션바에 새로운 스킬 슬롯 해금 및 자동 시전 마법진 전개</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>3. 선행 조건 필터 (prerequisite) 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>특정 조건을 만족했을 때만 3지선다 목록에 등장하도록 제어하는 필터입니다. (비어있으면 무조건 등장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>값 (Enum)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>등장 조건</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>기획 의도 및 목적</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>(빈칸)</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>조건 없음</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>처음부터 누구나 언제든 획득 가능한 기본 카드</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>has_summon</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>불사조 소환수 보유 시</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>소환수가 없는데 소환수 강화 카드가 나와서 선택지를 낭비하는 현상 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>has_meteor</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>유성낙하(메테오) 습득 시</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>메테오를 배우지 않은 상태에서 메테오 강화 카드가 뜨는 현상 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>has_combustion</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>발화(Combustion) 습득 시</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>발화 스킬을 배운 상태에서만 '발화의 화신' 등의 카드가 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>has_fireblast</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>화염 작렬 습득 시</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>화염 작렬 스킬 보유자에게만 전용 강화 카드 제공</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>4. 고대 주문서 해금 스킬 (spellKey) 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>build가 'spell'인 카드를 획득했을 때 즉시 플레이어에게 해금해 줄 스킬 식별자입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>값 (Enum)</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>해금되는 스킬명</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>스킬 유형</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>스킬 효과 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>autocast</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>비전 마법진 (자동 시전)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>패시브 마법진</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>발아래 마법진 전개, 쿨다운마다 배운 스킬 자동 연계 시전</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>fireblast</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>불꽃 작렬</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>보조 즉발기</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>시전 중에도 즉시 발사되는 100% 확정 치명타 마법</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>meteor</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>유성낙하 (메테오)</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>광역 궁극기</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>거대 운석 투하, 치명타 2연속(몰열) 시 즉시 노코스트 시전</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>combustion</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>발화</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>버프 극딜기</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>10초간 모든 마법 치명타 100% 확정 및 마력 폭주</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>불사조 정령</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>전투 소환수</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>항시 함께 전투하며 목표를 지속 공격하는 소환수 소환</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>ice_barrier</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>얼음 보호막</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>생존 방어기</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>최대 체력의 40% 보호막 생성 및 상태이상 방어</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>5. 특수 고유 메커니즘 (mechanic) 및 파라미터 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>단순 스탯 증가가 아닌 인게임 전투 시스템의 룰을 직접 변경하는 고유 특수 효과입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>기믹 키 (mechanic)</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>효과 명칭</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>동작 메커니즘 설명</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>기믹 파라미터 예시 (JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>split_fireball</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>화염구 2갈래 분열</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>화염구 시전 시 탄환이 2개로 갈라져 2번 타격합니다.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>없음 (단독 발동)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>haste_stack</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>가속도 중첩 버프</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>화염구 적중 시마다 가속도가 5%씩 최대 5중첩까지 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>gatling_mode</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>게틀링 머신건 모드</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>연속 시전 시 화염구 시전 시간이 0.4초까지 극한으로 단축됩니다.</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>chain_hot_streak</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>연쇄 몰아치는 열기</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>몰열 메테오 투하 시 지정된 확률로 몰열이 즉시 재발동합니다.</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>{"chainHotStreak": 0.4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>meteor_buff</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>거대 운석 폭격</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>메테오의 낙하 반경과 피해량이 2배로 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>combustion_god</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>발화의 절대자</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>발화 유지 시간이 5초 증가하고 치명타 피해가 50% 추가 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>extra_spirit</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>정령 군단 추가 소환</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>소환할 수 있는 정령의 수가 +1 증가하여 동시 출격합니다.</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>spirit_frenzy</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>정령 광란의 축제</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>정령의 공격 속도와 공격력이 대폭 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>{"spiritDamageMult": 1.4, "spiritSpeedMult": 1.5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>synchronized_fire</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>일제 사격 연계</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>마법사가 스킬을 시전할 때 소환수도 동일한 방향으로 동시 사격합니다.</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>cinder_lord</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>불씨의 군주</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>소환수 주변에 항시 불길이 피어올라 적에게 도트 피해를 입힙니다.</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>executioner</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>처형인의 일격</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>적 체력이 40% 이하일 때 가하는 모든 피해량이 증가합니다.</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>{"executionerMult": 0.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>phoenix_reset</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>불사조의 가호</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>치명타 적중 시 15% 확률로 모든 스킬의 쿨다운이 즉시 리셋됩니다.</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>6. 스탯 (stats) 컬럼 가이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>카드 습득 시 플레이어의 기본 능력치에 영구 누적되는 스탯 항목입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>열 이름</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>스탯 키</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>단위 및 계산 방식</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>인게임 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>주문력(sp)</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>sp</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>정수 (절대값)</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>모든 스킬(화염구, 메테오, 불꽃작렬)의 기본 피해량에 직접 가산</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>가속도(haste)</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>haste</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>% (백분율)</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>시전 바 진행 속도 증가 및 글로벌 쿨다운(GCD) 단축</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>치명타(crit)</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>crit</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>% (백분율)</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>모든 공격의 치명타 발생 확률 증가 (몰열 2연속 발동에 핵심 기여)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>치명피해(critDmg)</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>critDmg</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>% (백분율)</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>치명타 발생 시 기본 150% 피해량에 추가 가산</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>골드보너스(goldBonus)</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>goldBonus</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>% (백분율)</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>몬스터 처치 및 보스 격파 시 드롭되는 골드 획득량 증가</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A44:D44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -646,7 +646,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="79.83203125" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -1850,7 +1850,7 @@
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="67.1640625" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -1107,7 +1107,11 @@
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>has_meteor</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -1567,7 +1571,11 @@
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>has_any_spell</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1615,7 +1623,11 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>has_any_spell</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>autocast</t>
@@ -1824,8 +1836,8 @@
     <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 빌드" error="빌드는 rapid, crit, pet, util, spell 중에서 선택해주세요." promptTitle="[빌드(build) 분류 안내]" prompt="• rapid: 속사/가속 화염구 난사&#10;• crit: 극치명타 몰열 메테오 누킹&#10;• pet: 불사조 정령 군단&#10;• util: 생존력 및 골드 유틸&#10;• spell: 고대 주문서 스킬 해금" type="list">
       <formula1>"rapid,crit,pet,util,spell"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 선행조건" error="선행조건 목록에서 선택하거나 빈칸으로 두세요." promptTitle="[선행조건(prerequisite) 안내]" prompt="해당 조건이 달성되어야만 3지선다에 등장합니다:&#10;• has_summon: 소환수 보유 시&#10;• has_meteor: 메테오 습득 시&#10;• has_combustion: 발화 습득 시&#10;• (빈칸): 조건 없이 항상 등장" type="list">
-      <formula1>"has_summon,has_meteor,has_combustion,has_fireblast,has_ice_barrier"</formula1>
+    <dataValidation sqref="M2:M100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 선행조건" error="선행조건 목록에서 선택하거나 빈칸으로 두세요." promptTitle="[선행조건(prerequisite) 안내]" prompt="해당 조건이 달성되어야만 3지선다에 등장합니다:&#10;• has_summon: 소환수 보유 시&#10;• has_meteor: 메테오 습득 시&#10;• has_combustion: 발화 습득 시&#10;• has_any_spell: 쿨다운 보조 마법 1개 이상 습득 시&#10;• (빈칸): 조건 없이 항상 등장" type="list">
+      <formula1>"has_summon,has_meteor,has_combustion,has_fireblast,has_ice_barrier,has_any_spell"</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 스킬 키" error="해금스킬 키 목록에서 선택하거나 빈칸으로 두세요." promptTitle="[해금스킬(spellKey) 안내]" prompt="주문서 카드 습득 시 액션바에 해금할 스킬:&#10;• fireblast: 불꽃 작렬&#10;• meteor: 유성낙하&#10;• combustion: 발화&#10;• summon: 불사조 소환&#10;• ice_barrier: 얼음 보호막&#10;• autocast: 자동 시전 마법진" type="list">
       <formula1>"fireblast,meteor,combustion,summon,ice_barrier,autocast"</formula1>
@@ -1845,7 +1857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2209,7 +2221,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>메테오를 배우지 않은 상태에서 메테오 강화 카드가 뜨는 현상 방지</t>
+          <t>메테오를 배우지 않은 상태에서 메테오 강화/연쇄 몰열 카드가 뜨는 현상 방지</t>
         </is>
       </c>
     </row>
@@ -2247,615 +2259,632 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>has_any_spell</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>쿨다운 보조 마법 1개 이상 습득 시</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>쿨다운 스킬이 없는데 '자동 시전'이나 '쿨다운 초기화' 카드가 떠서 무용지물이 되는 현상 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>4. 고대 주문서 해금 스킬 (spellKey) 가이드</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>build가 'spell'인 카드를 획득했을 때 즉시 플레이어에게 해금해 줄 스킬 식별자입니다.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>값 (Enum)</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>해금되는 스킬명</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>스킬 유형</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>스킬 효과 요약</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>autocast</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>비전 마법진 (자동 시전)</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>패시브 마법진</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>발아래 마법진 전개, 쿨다운마다 배운 스킬 자동 연계 시전</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>fireblast</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>불꽃 작렬</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>보조 즉발기</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>시전 중에도 즉시 발사되는 100% 확정 치명타 마법</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>meteor</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>유성낙하 (메테오)</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>광역 궁극기</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>거대 운석 투하, 치명타 2연속(몰열) 시 즉시 노코스트 시전</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>combustion</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>발화</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>버프 극딜기</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>10초간 모든 마법 치명타 100% 확정 및 마력 폭주</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>summon</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>불사조 정령</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>전투 소환수</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>항시 함께 전투하며 목표를 지속 공격하는 소환수 소환</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="11" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>ice_barrier</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>얼음 보호막</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>생존 방어기</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>최대 체력의 40% 보호막 생성 및 상태이상 방어</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>5. 특수 고유 메커니즘 (mechanic) 및 파라미터 가이드</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>단순 스탯 증가가 아닌 인게임 전투 시스템의 룰을 직접 변경하는 고유 특수 효과입니다.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>기믹 키 (mechanic)</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>효과 명칭</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>동작 메커니즘 설명</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>기믹 파라미터 예시 (JSON)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>split_fireball</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>화염구 2갈래 분열</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>화염구 시전 시 탄환이 2개로 갈라져 2번 타격합니다.</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>없음 (단독 발동)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>haste_stack</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>가속도 중첩 버프</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>화염구 적중 시마다 가속도가 5%씩 최대 5중첩까지 증가합니다.</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>gatling_mode</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>게틀링 머신건 모드</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>연속 시전 시 화염구 시전 시간이 0.4초까지 극한으로 단축됩니다.</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>chain_hot_streak</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>연쇄 몰아치는 열기</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>몰열 메테오 투하 시 지정된 확률로 몰열이 즉시 재발동합니다.</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>{"chainHotStreak": 0.4}</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>meteor_buff</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>거대 운석 폭격</t>
         </is>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>메테오의 낙하 반경과 피해량이 2배로 증가합니다.</t>
         </is>
       </c>
-      <c r="D50" s="10" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>combustion_god</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>발화의 절대자</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>발화 유지 시간이 5초 증가하고 치명타 피해가 50% 추가 증가합니다.</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>extra_spirit</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>정령 군단 추가 소환</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>소환할 수 있는 정령의 수가 +1 증가하여 동시 출격합니다.</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>spirit_frenzy</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>정령 광란의 축제</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>정령의 공격 속도와 공격력이 대폭 증가합니다.</t>
         </is>
       </c>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>{"spiritDamageMult": 1.4, "spiritSpeedMult": 1.5}</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>synchronized_fire</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>일제 사격 연계</t>
         </is>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>마법사가 스킬을 시전할 때 소환수도 동일한 방향으로 동시 사격합니다.</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>cinder_lord</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>불씨의 군주</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C56" s="13" t="inlineStr">
         <is>
           <t>소환수 주변에 항시 불길이 피어올라 적에게 도트 피해를 입힙니다.</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>executioner</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>처형인의 일격</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>적 체력이 40% 이하일 때 가하는 모든 피해량이 증가합니다.</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>{"executionerMult": 0.7}</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>phoenix_reset</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>불사조의 가호</t>
         </is>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>치명타 적중 시 15% 확률로 모든 스킬의 쿨다운이 즉시 리셋됩니다.</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>6. 스탯 (stats) 컬럼 가이드</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>카드 습득 시 플레이어의 기본 능력치에 영구 누적되는 스탯 항목입니다.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>열 이름</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>스탯 키</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>단위 및 계산 방식</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>인게임 효과</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>주문력(sp)</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>sp</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>정수 (절대값)</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>모든 스킬(화염구, 메테오, 불꽃작렬)의 기본 피해량에 직접 가산</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>가속도(haste)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>haste</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>% (백분율)</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>시전 바 진행 속도 증가 및 글로벌 쿨다운(GCD) 단축</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>치명타(crit)</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>crit</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>% (백분율)</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>모든 공격의 치명타 발생 확률 증가 (몰열 2연속 발동에 핵심 기여)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>치명피해(critDmg)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>critDmg</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>% (백분율)</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>치명타 발생 시 기본 150% 피해량에 추가 가산</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>골드보너스(goldBonus)</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>goldBonus</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>% (백분율)</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>몬스터 처치 및 보스 격파 시 드롭되는 골드 획득량 증가</t>
         </is>
@@ -2863,16 +2892,16 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A61:D61"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A44:D44"/>
   </mergeCells>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tak\Projects\dps-fire-mage\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AA7B61-70F3-4DCF-934C-AFF0019BDA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D217724-52E5-46F6-9786-825AEC26AB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-36260" yWindow="1630" windowWidth="30020" windowHeight="17950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -383,9 +383,6 @@
     <t>🌀</t>
   </si>
   <si>
-    <t>화염구 시전 완료 시 4초간 시전 속도가 &lt;b&gt;+15%&lt;/b&gt; 가속됩니다 (최대 5중첩).</t>
-  </si>
-  <si>
     <t>haste_stack</t>
   </si>
   <si>
@@ -1059,6 +1056,10 @@
   </si>
   <si>
     <t>몬스터 처치 및 보스 격파 시 드롭되는 골드 획득량 증가</t>
+  </si>
+  <si>
+    <t>화염구 시전 완료 시 4초간 시전 속도가 &lt;b&gt;+15%&lt;/b&gt; 가속됩니다 (최대 2중첩).</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1749,7 +1750,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>35</v>
+        <v>260</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -1759,22 +1760,22 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:16" ht="24" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="15" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>40</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>20</v>
@@ -1783,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -1793,31 +1794,31 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" ht="24" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" s="3">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -1833,25 +1834,25 @@
     </row>
     <row r="8" spans="1:16" ht="24" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -1867,25 +1868,25 @@
     </row>
     <row r="9" spans="1:16" ht="24" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" s="3">
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -1893,37 +1894,37 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="C10" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" s="3">
         <v>2</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -1931,35 +1932,35 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:16" ht="24" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="D11" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -1967,20 +1968,20 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:16" ht="24" customHeight="1">
       <c r="A12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>24</v>
@@ -1989,13 +1990,13 @@
         <v>19</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F12" s="3">
         <v>4</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2005,31 +2006,31 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:16" ht="24" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F13" s="3">
         <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -2037,37 +2038,37 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="24" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -2075,35 +2076,35 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P14" s="2"/>
     </row>
     <row r="15" spans="1:16" ht="24" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="D15" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -2111,35 +2112,35 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P15" s="2"/>
     </row>
     <row r="16" spans="1:16" ht="24" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="3">
         <v>3</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -2153,25 +2154,25 @@
     </row>
     <row r="17" spans="1:16" ht="24" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F17" s="3">
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -2181,33 +2182,33 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="24" customHeight="1">
       <c r="A18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="D18" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -2215,35 +2216,35 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P18" s="2"/>
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1">
       <c r="A19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -2251,20 +2252,20 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
     </row>
     <row r="20" spans="1:16" ht="24" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>28</v>
@@ -2273,13 +2274,13 @@
         <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -2288,32 +2289,32 @@
       <c r="L20" s="3"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>29</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F21" s="3">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -2322,20 +2323,20 @@
       <c r="L21" s="3"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>29</v>
@@ -2347,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -2356,32 +2357,32 @@
       <c r="L22" s="3"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
     </row>
     <row r="23" spans="1:16" ht="24" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -2390,7 +2391,7 @@
       <c r="L23" s="3"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -2431,12 +2432,12 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21">
       <c r="A1" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="26" customHeight="1">
       <c r="A3" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -2444,7 +2445,7 @@
     </row>
     <row r="4" spans="1:4" ht="20" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2452,16 +2453,16 @@
     </row>
     <row r="5" spans="1:4" ht="24" customHeight="1">
       <c r="A5" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
@@ -2469,13 +2470,13 @@
         <v>19</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="22" customHeight="1">
@@ -2483,46 +2484,46 @@
         <v>29</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>140</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="22" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>144</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="22" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="26" customHeight="1">
       <c r="A12" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2530,7 +2531,7 @@
     </row>
     <row r="13" spans="1:4" ht="20" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2538,16 +2539,16 @@
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
       <c r="A14" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>133</v>
-      </c>
       <c r="C14" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="22" customHeight="1">
@@ -2555,165 +2556,165 @@
         <v>20</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="22" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="22" customHeight="1">
       <c r="A17" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="22" customHeight="1">
       <c r="A18" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="22" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="26" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
     </row>
     <row r="24" spans="1:4" ht="24" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="22" customHeight="1">
       <c r="A25" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>176</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="22" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="22" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>180</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="22" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B28" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="22" customHeight="1">
       <c r="A29" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>185</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="22" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>187</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="26" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -2721,7 +2722,7 @@
     </row>
     <row r="34" spans="1:4" ht="20" customHeight="1">
       <c r="A34" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2729,105 +2730,105 @@
     </row>
     <row r="35" spans="1:4" ht="24" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="22" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="22" customHeight="1">
       <c r="A37" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B37" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="D37" s="11" t="s">
         <v>198</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="22" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="D38" s="8" t="s">
         <v>201</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="22" customHeight="1">
       <c r="A39" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B39" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="D39" s="11" t="s">
         <v>204</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="22" customHeight="1">
       <c r="A40" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="D40" s="8" t="s">
         <v>207</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="22" customHeight="1">
       <c r="A41" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="C41" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="D41" s="11" t="s">
         <v>211</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="26" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -2835,7 +2836,7 @@
     </row>
     <row r="45" spans="1:4" ht="20" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
@@ -2843,16 +2844,16 @@
     </row>
     <row r="46" spans="1:4" ht="24" customHeight="1">
       <c r="A46" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="22" customHeight="1">
@@ -2860,172 +2861,172 @@
         <v>31</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>220</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="22" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C48" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>223</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="22" customHeight="1">
       <c r="A49" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>226</v>
-      </c>
       <c r="D49" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="22" customHeight="1">
       <c r="A50" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="22" customHeight="1">
       <c r="A51" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>230</v>
-      </c>
       <c r="D51" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="22" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C52" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>232</v>
-      </c>
       <c r="D52" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="22" customHeight="1">
       <c r="A53" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>234</v>
-      </c>
       <c r="D53" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="22" customHeight="1">
       <c r="A54" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="22" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>238</v>
-      </c>
       <c r="D55" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="22" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B56" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C56" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>240</v>
-      </c>
       <c r="D56" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="22" customHeight="1">
       <c r="A57" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="22" customHeight="1">
       <c r="A58" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="26" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B61" s="13"/>
       <c r="C61" s="13"/>
@@ -3033,7 +3034,7 @@
     </row>
     <row r="62" spans="1:4" ht="20" customHeight="1">
       <c r="A62" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -3041,16 +3042,16 @@
     </row>
     <row r="63" spans="1:4" ht="24" customHeight="1">
       <c r="A63" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="C63" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>248</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="22" customHeight="1">
@@ -3058,13 +3059,13 @@
         <v>7</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="D64" s="8" t="s">
         <v>251</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="22" customHeight="1">
@@ -3072,13 +3073,13 @@
         <v>8</v>
       </c>
       <c r="B65" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C65" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="D65" s="11" t="s">
         <v>254</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="22" customHeight="1">
@@ -3086,13 +3087,13 @@
         <v>9</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="22" customHeight="1">
@@ -3100,13 +3101,13 @@
         <v>10</v>
       </c>
       <c r="B67" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D67" s="11" t="s">
         <v>257</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="22" customHeight="1">
@@ -3114,13 +3115,13 @@
         <v>11</v>
       </c>
       <c r="B68" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D68" s="8" t="s">
         <v>259</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -2299,7 +2299,7 @@
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>치명타가 남기는 &lt;b&gt;화상 피해가 2.5배&lt;/b&gt;로 불어납니다.</t>
+          <t>&lt;b&gt;모든 적중이 화상&lt;/b&gt;을 남기고, 치명타가 남기는 &lt;b&gt;화상 피해는 6배&lt;/b&gt;로 불어납니다. 쓰러진 적의 &lt;b&gt;남은 화상은 다음 적에게 번집니다&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>Ignite left by critical strikes deals &lt;b&gt;2.5x damage&lt;/b&gt;.</t>
+          <t>&lt;b&gt;Every hit leaves Ignite&lt;/b&gt;, and Ignite from critical strikes deals &lt;b&gt;6x damage&lt;/b&gt;. Leftover Ignite &lt;b&gt;spreads to the next enemy&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="S24" s="19" t="inlineStr">
         <is>
-          <t>{"igniteRatioMult": 2.5}</t>
+          <t>{"igniteRatioMult": 6, "igniteOnAllHits": true, "igniteCarryOver": true}</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;불사조&lt;/b&gt;가 함께 싸우며 확정 치명타로 협공하고, 치명타 적중 시 &lt;b&gt;15% 확률로 모든 스킬 쿨다운&lt;/b&gt;이 초기화됩니다.</t>
+          <t>&lt;b&gt;불사조&lt;/b&gt;가 함께 싸우며 확정 치명타로 협공하고, 치명타 적중 시 &lt;b&gt;10% 확률로 모든 스킬 쿨다운&lt;/b&gt;이 초기화됩니다.</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>A &lt;b&gt;Phoenix&lt;/b&gt; fights at your side with guaranteed crits, and your crits have a &lt;b&gt;15% chance to reset all skill cooldowns&lt;/b&gt;.</t>
+          <t>A &lt;b&gt;Phoenix&lt;/b&gt; fights at your side with guaranteed crits, and your crits have a &lt;b&gt;10% chance to reset all skill cooldowns&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr"/>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C54" s="27" t="inlineStr">
         <is>
-          <t>치명타가 남기는 화상(치명타 피해의 22%)을 igniteRatioMult배로 키웁니다.</t>
+          <t>모든 적중이 화상(피해의 22%)을 남기고, 치명타 화상은 igniteRatioMult배로 키웁니다. igniteCarryOver면 쓰러진 적의 남은 화상이 다음 적에게 이어집니다.</t>
         </is>
       </c>
       <c r="D54" s="27" t="inlineStr">
         <is>
-          <t>{"igniteRatioMult": 2.5}</t>
+          <t>{"igniteRatioMult": 6, "igniteOnAllHits": true, "igniteCarryOver": true}</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C56" s="27" t="inlineStr">
         <is>
-          <t>불사조가 2.4초마다 확정 치명타로 협공하고, 치명타 적중 시 15% 확률로 모든 스킬의 재사용 대기가 초기화됩니다.</t>
+          <t>불사조가 2.4초마다 확정 치명타로 협공하고, 치명타 적중 시 10% 확률로 모든 스킬의 재사용 대기가 초기화됩니다.</t>
         </is>
       </c>
       <c r="D56" s="27" t="inlineStr">

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="13" customWidth="1" style="13" min="1" max="1"/>
@@ -2573,6 +2573,69 @@
       </c>
       <c r="S28" s="19" t="inlineStr"/>
     </row>
+    <row r="29" ht="24" customHeight="1" s="13">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>util_auto_grimoire</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>자동 영창</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>화염구 외 모든 주문(불꽃 작렬·메테오·마력 폭주·불장판)이 &lt;b&gt;최적의 순간에 자동 시전&lt;/b&gt;됩니다. 주문 칸의 &lt;b&gt;AUTO&lt;/b&gt;를 눌러 주문별로 끄고 켤 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="inlineStr">
+        <is>
+          <t>Auto-Incantation</t>
+        </is>
+      </c>
+      <c r="I29" s="19" t="inlineStr">
+        <is>
+          <t>Every spell besides Fireball (Fire Blast, Meteor, Combustion, Flame Patch) &lt;b&gt;casts itself at the perfect moment&lt;/b&gt;. Tap a slot's &lt;b&gt;AUTO&lt;/b&gt; tag to toggle each spell.</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr"/>
+      <c r="K29" s="20" t="inlineStr"/>
+      <c r="L29" s="20" t="inlineStr"/>
+      <c r="M29" s="20" t="inlineStr"/>
+      <c r="N29" s="20" t="inlineStr"/>
+      <c r="O29" s="20" t="inlineStr"/>
+      <c r="P29" s="19" t="inlineStr">
+        <is>
+          <t>has_any_spell</t>
+        </is>
+      </c>
+      <c r="Q29" s="19" t="inlineStr"/>
+      <c r="R29" s="19" t="inlineStr">
+        <is>
+          <t>smart_autocast</t>
+        </is>
+      </c>
+      <c r="S29" s="19" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 값" error="목록(common, rare, legendary)에서 선택해주세요." promptTitle="[희귀도(rarity) 옵션 안내]" prompt="• common: 일반&#10;• rare: 희귀&#10;• legendary: 전설 (보스전 우대)" type="list">
@@ -2587,8 +2650,8 @@
     <dataValidation sqref="Q2:Q100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(fireblast, meteor, combustion, flame_patch)에서 선택하거나 빈칸으로 두세요." promptTitle="[해금스킬(spellKey) 안내]" prompt="• fireblast: 불꽃 작렬&#10;• meteor: 메테오&#10;• combustion: 마력 폭주&#10;• flame_patch: 불장판" type="list">
       <formula1>"fireblast,meteor,combustion,flame_patch"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(split_fireball, gatling_mode, quickdraw_charge, meteor_buff, meteor_charge, combustion_god, extra_spirit, synchronized_fire, cinder_lord, patch_boost, wildfire, executioner, phoenix_reset)에서 선택하거나 빈칸으로 두세요." promptTitle="[특수기믹(mechanic) 안내]" prompt="시스템 특수 로직 키입니다.&#10;효과와 파라미터는 [📖 옵션_도움말_가이드] 탭을 확인하세요!" type="list">
-      <formula1>"split_fireball,gatling_mode,quickdraw_charge,meteor_buff,meteor_charge,combustion_god,extra_spirit,synchronized_fire,cinder_lord,patch_boost,wildfire,executioner,phoenix_reset"</formula1>
+    <dataValidation sqref="R2:R100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(split_fireball, gatling_mode, quickdraw_charge, meteor_buff, meteor_charge, combustion_god, extra_spirit, synchronized_fire, cinder_lord, patch_boost, wildfire, executioner, phoenix_reset, smart_autocast)에서 선택하거나 빈칸으로 두세요." promptTitle="[특수기믹(mechanic) 안내]" prompt="시스템 특수 로직 키입니다.&#10;효과와 파라미터는 [📖 옵션_도움말_가이드] 탭을 확인하세요!" type="list">
+      <formula1>"split_fireball,gatling_mode,quickdraw_charge,meteor_buff,meteor_charge,combustion_god,extra_spirit,synchronized_fire,cinder_lord,patch_boost,wildfire,executioner,phoenix_reset,smart_autocast"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2602,7 +2665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="13" min="1" max="1"/>
@@ -3445,169 +3508,191 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="26" customHeight="1" s="13">
-      <c r="A59" s="22" t="inlineStr">
+    <row r="57" ht="22" customHeight="1" s="13">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>smart_autocast</t>
+        </is>
+      </c>
+      <c r="B57" s="29" t="inlineStr">
+        <is>
+          <t>자동 영창</t>
+        </is>
+      </c>
+      <c r="C57" s="30" t="inlineStr">
+        <is>
+          <t>화염구 외 주문(불꽃 작렬·메테오·마력 폭주·불장판)도 최적의 순간에 자동 시전합니다. 없으면 이 주문들은 직접 눌러야 합니다.</t>
+        </is>
+      </c>
+      <c r="D57" s="30" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1" s="13">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>6. 스탯 (stats) 컬럼 가이드</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1" s="13">
-      <c r="A60" s="23" t="inlineStr">
+    <row r="61" ht="20" customHeight="1" s="13">
+      <c r="A61" s="23" t="inlineStr">
         <is>
           <t>카드 습득 시 런(Run) 동안 누적되는 스탯입니다. 모든 값은 정수 퍼센트로 입력하며, 대가형 카드는 음수로 손해를 표현합니다.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1" s="13">
-      <c r="A61" s="24" t="inlineStr">
+    <row r="62" ht="24" customHeight="1" s="13">
+      <c r="A62" s="24" t="inlineStr">
         <is>
           <t>열 이름</t>
         </is>
       </c>
-      <c r="B61" s="24" t="inlineStr">
+      <c r="B62" s="24" t="inlineStr">
         <is>
           <t>스탯 키</t>
         </is>
       </c>
-      <c r="C61" s="24" t="inlineStr">
+      <c r="C62" s="24" t="inlineStr">
         <is>
           <t>단위 및 계산 방식</t>
         </is>
       </c>
-      <c r="D61" s="24" t="inlineStr">
+      <c r="D62" s="24" t="inlineStr">
         <is>
           <t>인게임 효과</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="22" customHeight="1" s="13">
-      <c r="A62" s="25" t="inlineStr">
+    <row r="63" ht="22" customHeight="1" s="13">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t>주문력%(spPct)</t>
         </is>
       </c>
-      <c r="B62" s="26" t="inlineStr">
+      <c r="B63" s="26" t="inlineStr">
         <is>
           <t>spPct</t>
         </is>
       </c>
-      <c r="C62" s="27" t="inlineStr">
+      <c r="C63" s="27" t="inlineStr">
         <is>
           <t>% (예: 15 = +15%)</t>
         </is>
       </c>
-      <c r="D62" s="27" t="inlineStr">
+      <c r="D63" s="27" t="inlineStr">
         <is>
           <t>기본 주문력 100에 곱해져 모든 피해량이 증가</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="22" customHeight="1" s="13">
-      <c r="A63" s="28" t="inlineStr">
+    <row r="64" ht="22" customHeight="1" s="13">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>가속%(haste)</t>
         </is>
       </c>
-      <c r="B63" s="29" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>haste</t>
         </is>
       </c>
-      <c r="C63" s="30" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>% (예: 20 = +20%)</t>
         </is>
       </c>
-      <c r="D63" s="30" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>시전 바 진행 속도·소환수 공격 주기·불꽃 작렬 충전 속도 증가</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="22" customHeight="1" s="13">
-      <c r="A64" s="25" t="inlineStr">
+    <row r="65" ht="22" customHeight="1" s="13">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>치명타%(crit)</t>
         </is>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="B65" s="26" t="inlineStr">
         <is>
           <t>crit</t>
         </is>
       </c>
-      <c r="C64" s="27" t="inlineStr">
+      <c r="C65" s="27" t="inlineStr">
         <is>
           <t>%p (예: 10 = +10%, 기본 5%)</t>
         </is>
       </c>
-      <c r="D64" s="27" t="inlineStr">
+      <c r="D65" s="27" t="inlineStr">
         <is>
           <t>모든 공격의 치명타 확률 증가 (몰열 2연속 발동에 핵심 기여)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="22" customHeight="1" s="13">
-      <c r="A65" s="28" t="inlineStr">
+    <row r="66" ht="22" customHeight="1" s="13">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>치명피해%(critDmg)</t>
         </is>
       </c>
-      <c r="B65" s="29" t="inlineStr">
+      <c r="B66" s="29" t="inlineStr">
         <is>
           <t>critDmg</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
         <is>
           <t>% (예: 35 = +35%)</t>
         </is>
       </c>
-      <c r="D65" s="30" t="inlineStr">
+      <c r="D66" s="30" t="inlineStr">
         <is>
           <t>치명타 발생 시 기본 150% 피해 배율에 가산</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1" s="13">
-      <c r="A66" s="25" t="inlineStr">
+    <row r="67" ht="22" customHeight="1" s="13">
+      <c r="A67" s="25" t="inlineStr">
         <is>
           <t>지속피해%(burnPct)</t>
         </is>
       </c>
-      <c r="B66" s="26" t="inlineStr">
+      <c r="B67" s="26" t="inlineStr">
         <is>
           <t>burnPct</t>
         </is>
       </c>
-      <c r="C66" s="27" t="inlineStr">
+      <c r="C67" s="27" t="inlineStr">
         <is>
           <t>% (예: 45 = +45%)</t>
         </is>
       </c>
-      <c r="D66" s="27" t="inlineStr">
+      <c r="D67" s="27" t="inlineStr">
         <is>
           <t>화상·메테오 연소·불장판 지속 피해 증가</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1" s="13">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="68" ht="22" customHeight="1" s="13">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>소환수%(spiritPct)</t>
         </is>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>spiritPct</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>% (예: 40 = +40%)</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>화염 정령·불사조 피해 증가</t>
         </is>
@@ -3615,11 +3700,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A11:D11"/>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -1460,7 +1460,11 @@
       </c>
       <c r="N10" s="20" t="inlineStr"/>
       <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="19" t="inlineStr"/>
+      <c r="P10" s="19" t="inlineStr">
+        <is>
+          <t>crit_after_15</t>
+        </is>
+      </c>
       <c r="Q10" s="19" t="inlineStr"/>
       <c r="R10" s="19" t="inlineStr"/>
       <c r="S10" s="19" t="inlineStr"/>
@@ -2644,8 +2648,8 @@
     <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 값" error="목록(rapid, crit, summon, burn, utility)에서 선택해주세요." promptTitle="[빌드(build) 분류 안내]" prompt="• rapid: 속사 머신건&#10;• crit: 극치명 누킹&#10;• summon: 정령 군단&#10;• burn: 연소 지대&#10;• utility: 유틸리티" type="list">
       <formula1>"rapid,crit,summon,burn,utility"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(has_summon, has_meteor, has_combustion, has_flame_patch, has_any_spell)에서 선택하거나 빈칸으로 두세요." promptTitle="[선행조건(prerequisite) 안내]" prompt="조건을 달성해야 3지선다에 등장합니다.&#10;빈칸이면 조건 없이 항상 등장합니다." type="list">
-      <formula1>"has_summon,has_meteor,has_combustion,has_flame_patch,has_any_spell"</formula1>
+    <dataValidation sqref="P2:P100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(has_summon, has_meteor, has_combustion, has_flame_patch, has_any_spell, crit_after_15)에서 선택하거나 빈칸으로 두세요." promptTitle="[선행조건(prerequisite) 안내]" prompt="조건을 달성해야 3지선다에 등장합니다.&#10;빈칸이면 조건 없이 항상 등장합니다." type="list">
+      <formula1>"has_summon,has_meteor,has_combustion,has_flame_patch,has_any_spell,crit_after_15"</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(fireblast, meteor, combustion, flame_patch)에서 선택하거나 빈칸으로 두세요." promptTitle="[해금스킬(spellKey) 안내]" prompt="• fireblast: 불꽃 작렬&#10;• meteor: 메테오&#10;• combustion: 마력 폭주&#10;• flame_patch: 불장판" type="list">
       <formula1>"fireblast,meteor,combustion,flame_patch"</formula1>
@@ -2665,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="13" min="1" max="1"/>
@@ -3062,637 +3066,654 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1" s="13">
-      <c r="A32" s="22" t="inlineStr">
+    <row r="30" ht="22" customHeight="1" s="13">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>crit_after_15</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>카드를 받은 뒤에도 치명타 확률 15% 이상</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>기본 치명타 5%에서 '무모한 일격'(-8%)을 골라 치명타가 0%가 되는 함정 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1" s="13">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>4. 고대 주문서 해금 스킬 (spellKey) 가이드</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1" s="13">
-      <c r="A33" s="23" t="inlineStr">
+    <row r="34" ht="20" customHeight="1" s="13">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>주문서 카드를 획득했을 때 즉시 해금해 줄 스킬입니다. 이미 습득한 주문서는 3지선다에 다시 등장하지 않습니다. (자동 시전은 처음부터 기본 제공)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="24" customHeight="1" s="13">
-      <c r="A34" s="24" t="inlineStr">
+    <row r="35" ht="24" customHeight="1" s="13">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>값 (Enum)</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>해금되는 스킬명</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>스킬 유형</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>스킬 효과 요약</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1" s="13">
-      <c r="A35" s="25" t="inlineStr">
+    <row r="36" ht="22" customHeight="1" s="13">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>fireblast</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>불꽃 작렬</t>
         </is>
       </c>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>보조 즉발기</t>
         </is>
       </c>
-      <c r="D35" s="27" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>시전 중에도 즉시 발사되는 주문력 120% 확정 치명타 (2회 충전, 충전 8초)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1" s="13">
-      <c r="A36" s="28" t="inlineStr">
+    <row r="37" ht="22" customHeight="1" s="13">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>meteor</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr">
         <is>
           <t>메테오</t>
         </is>
       </c>
-      <c r="C36" s="30" t="inlineStr">
+      <c r="C37" s="30" t="inlineStr">
         <is>
           <t>강타기</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
+      <c r="D37" s="30" t="inlineStr">
         <is>
           <t>주문력 320% 운석 투하 및 6초 연소, 치명타 2연속(몰열) 시 즉시 노코스트 시전</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1" s="13">
-      <c r="A37" s="25" t="inlineStr">
+    <row r="38" ht="22" customHeight="1" s="13">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>combustion</t>
         </is>
       </c>
-      <c r="B37" s="26" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>마력 폭주</t>
         </is>
       </c>
-      <c r="C37" s="27" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>버프 극딜기</t>
         </is>
       </c>
-      <c r="D37" s="27" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>5초간 모든 마법 치명타 100% 확정 및 시전 속도 +20% (재사용 30초)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1" s="13">
-      <c r="A38" s="28" t="inlineStr">
+    <row r="39" ht="22" customHeight="1" s="13">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>flame_patch</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B39" s="29" t="inlineStr">
         <is>
           <t>불장판</t>
         </is>
       </c>
-      <c r="C38" s="30" t="inlineStr">
+      <c r="C39" s="30" t="inlineStr">
         <is>
           <t>지속 피해기</t>
         </is>
       </c>
-      <c r="D38" s="30" t="inlineStr">
+      <c r="D39" s="30" t="inlineStr">
         <is>
           <t>몬스터 발밑에 7초간 화염 지대 생성, 0.5초마다 주문력 50% 피해 (재사용 10초)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1" s="13">
-      <c r="A41" s="22" t="inlineStr">
+    <row r="42" ht="26" customHeight="1" s="13">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>5. 특수 고유 메커니즘 (mechanic) 및 파라미터 가이드</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1" s="13">
-      <c r="A42" s="23" t="inlineStr">
+    <row r="43" ht="20" customHeight="1" s="13">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>단순 스탯 증가가 아닌 전투 규칙을 바꾸는 효과입니다. 충전형은 스테이지 시작마다 충전이 다시 채워집니다.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="24" customHeight="1" s="13">
-      <c r="A43" s="24" t="inlineStr">
+    <row r="44" ht="24" customHeight="1" s="13">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>기믹 키 (mechanic)</t>
         </is>
       </c>
-      <c r="B43" s="24" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
         <is>
           <t>효과 명칭</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C44" s="24" t="inlineStr">
         <is>
           <t>동작 메커니즘 설명</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>기믹 파라미터 예시 (JSON)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1" s="13">
-      <c r="A44" s="25" t="inlineStr">
+    <row r="45" ht="22" customHeight="1" s="13">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>split_fireball</t>
         </is>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>분열 화염구</t>
         </is>
       </c>
-      <c r="C44" s="27" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>화염구 적중 시 작은 불씨가 분열되어 추가 타격합니다. (스택당 2개, 최대 6개, 각 주문력 40%)</t>
         </is>
       </c>
-      <c r="D44" s="27" t="inlineStr">
+      <c r="D45" s="27" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1" s="13">
-      <c r="A45" s="28" t="inlineStr">
+    <row r="46" ht="22" customHeight="1" s="13">
+      <c r="A46" s="28" t="inlineStr">
         <is>
           <t>gatling_mode</t>
         </is>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <t>화염 기관총</t>
         </is>
       </c>
-      <c r="C45" s="30" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>화염구 기본 시전 시간과 공통 대기 시간이 0.3초로 단축됩니다. (최소 0.12초)</t>
         </is>
       </c>
-      <c r="D45" s="30" t="inlineStr">
+      <c r="D46" s="30" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="22" customHeight="1" s="13">
-      <c r="A46" s="25" t="inlineStr">
+    <row r="47" ht="22" customHeight="1" s="13">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>quickdraw_charge</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>속사 장전 (충전형)</t>
         </is>
       </c>
-      <c r="C46" s="27" t="inlineStr">
+      <c r="C47" s="27" t="inlineStr">
         <is>
           <t>스테이지 시작마다 화염구를 시전 없이 즉시 발사하는 충전을 얻습니다. (중첩 시 충전 합산)</t>
         </is>
       </c>
-      <c r="D46" s="27" t="inlineStr">
+      <c r="D47" s="27" t="inlineStr">
         <is>
           <t>{"charges": 4}</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1" s="13">
-      <c r="A47" s="28" t="inlineStr">
+    <row r="48" ht="22" customHeight="1" s="13">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>meteor_buff</t>
         </is>
       </c>
-      <c r="B47" s="29" t="inlineStr">
+      <c r="B48" s="29" t="inlineStr">
         <is>
           <t>태양석 메테오</t>
         </is>
       </c>
-      <c r="C47" s="30" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>메테오를 습득시키고, 스택당 재사용 대기 50% 감소(최소 4초)·피해 +60%가 적용됩니다.</t>
         </is>
       </c>
-      <c r="D47" s="30" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1" s="13">
-      <c r="A48" s="25" t="inlineStr">
+    <row r="49" ht="22" customHeight="1" s="13">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>meteor_charge</t>
         </is>
       </c>
-      <c r="B48" s="26" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>잠열 충전 (충전형)</t>
         </is>
       </c>
-      <c r="C48" s="27" t="inlineStr">
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>스테이지 시작마다 메테오 피해 증폭 충전을 얻습니다. 메테오 발사 시 1회씩 소모됩니다.</t>
         </is>
       </c>
-      <c r="D48" s="27" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>{"charges": 3, "damageBonus": 1.5}</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1" s="13">
-      <c r="A49" s="28" t="inlineStr">
+    <row r="50" ht="22" customHeight="1" s="13">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>combustion_god</t>
         </is>
       </c>
-      <c r="B49" s="29" t="inlineStr">
+      <c r="B50" s="29" t="inlineStr">
         <is>
           <t>진홍의 마력 폭주</t>
         </is>
       </c>
-      <c r="C49" s="30" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>마력 폭주를 습득시키고, 지속시간 2배·폭주 중 모든 피해 2.5배가 적용됩니다.</t>
         </is>
       </c>
-      <c r="D49" s="30" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1" s="13">
-      <c r="A50" s="25" t="inlineStr">
+    <row r="51" ht="22" customHeight="1" s="13">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>extra_spirit</t>
         </is>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>화염 정령 소환</t>
         </is>
       </c>
-      <c r="C50" s="27" t="inlineStr">
+      <c r="C51" s="27" t="inlineStr">
         <is>
           <t>화염 정령을 1기 추가 소환합니다. (최대 4기, 1.3초마다 주문력 45% x 정령 수 피해)</t>
         </is>
       </c>
-      <c r="D50" s="27" t="inlineStr">
+      <c r="D51" s="27" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1" s="13">
-      <c r="A51" s="28" t="inlineStr">
+    <row r="52" ht="22" customHeight="1" s="13">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>synchronized_fire</t>
         </is>
       </c>
-      <c r="B51" s="29" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>일제 협공 사격</t>
         </is>
       </c>
-      <c r="C51" s="30" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>마법사가 화염구를 발사할 때마다 모든 정령이 동시에 협공합니다.</t>
         </is>
       </c>
-      <c r="D51" s="30" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="22" customHeight="1" s="13">
-      <c r="A52" s="25" t="inlineStr">
+    <row r="53" ht="22" customHeight="1" s="13">
+      <c r="A53" s="25" t="inlineStr">
         <is>
           <t>cinder_lord</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>잿더미 군단장</t>
         </is>
       </c>
-      <c r="C52" s="27" t="inlineStr">
+      <c r="C53" s="27" t="inlineStr">
         <is>
           <t>소환수 1기당 마법사의 모든 주문 피해가 +30% 증폭됩니다.</t>
         </is>
       </c>
-      <c r="D52" s="27" t="inlineStr">
+      <c r="D53" s="27" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1" s="13">
-      <c r="A53" s="28" t="inlineStr">
+    <row r="54" ht="22" customHeight="1" s="13">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>patch_boost</t>
         </is>
       </c>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>번지는 불길</t>
         </is>
       </c>
-      <c r="C53" s="30" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>불장판 재사용 대기시간에 cooldownMult를 곱하고 불장판 피해를 damageBonus만큼 증가시킵니다.</t>
         </is>
       </c>
-      <c r="D53" s="30" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>{"cooldownMult": 0.7, "damageBonus": 0.5}</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="22" customHeight="1" s="13">
-      <c r="A54" s="25" t="inlineStr">
+    <row r="55" ht="22" customHeight="1" s="13">
+      <c r="A55" s="25" t="inlineStr">
         <is>
           <t>wildfire</t>
         </is>
       </c>
-      <c r="B54" s="26" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>들불</t>
         </is>
       </c>
-      <c r="C54" s="27" t="inlineStr">
+      <c r="C55" s="27" t="inlineStr">
         <is>
           <t>모든 적중이 화상(피해의 22%)을 남기고, 치명타 화상은 igniteRatioMult배로 키웁니다. igniteCarryOver면 쓰러진 적의 남은 화상이 다음 적에게 이어집니다.</t>
         </is>
       </c>
-      <c r="D54" s="27" t="inlineStr">
+      <c r="D55" s="27" t="inlineStr">
         <is>
           <t>{"igniteRatioMult": 6, "igniteOnAllHits": true, "igniteCarryOver": true}</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="22" customHeight="1" s="13">
-      <c r="A55" s="28" t="inlineStr">
+    <row r="56" ht="22" customHeight="1" s="13">
+      <c r="A56" s="28" t="inlineStr">
         <is>
           <t>executioner</t>
         </is>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>처형인의 불꽃</t>
         </is>
       </c>
-      <c r="C55" s="30" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>적 체력이 40% 이하일 때 모든 피해량이 executionerMult만큼 증가합니다. (스택 시 합산)</t>
         </is>
       </c>
-      <c r="D55" s="30" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>{"executionerMult": 0.7}</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="22" customHeight="1" s="13">
-      <c r="A56" s="25" t="inlineStr">
+    <row r="57" ht="22" customHeight="1" s="13">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>phoenix_reset</t>
         </is>
       </c>
-      <c r="B56" s="26" t="inlineStr">
+      <c r="B57" s="26" t="inlineStr">
         <is>
           <t>불사조의 가호</t>
         </is>
       </c>
-      <c r="C56" s="27" t="inlineStr">
+      <c r="C57" s="27" t="inlineStr">
         <is>
           <t>불사조가 2.4초마다 확정 치명타로 협공하고, 치명타 적중 시 10% 확률로 모든 스킬의 재사용 대기가 초기화됩니다.</t>
         </is>
       </c>
-      <c r="D56" s="27" t="inlineStr">
+      <c r="D57" s="27" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="22" customHeight="1" s="13">
-      <c r="A57" s="28" t="inlineStr">
+    <row r="58" ht="22" customHeight="1" s="13">
+      <c r="A58" s="28" t="inlineStr">
         <is>
           <t>smart_autocast</t>
         </is>
       </c>
-      <c r="B57" s="29" t="inlineStr">
+      <c r="B58" s="29" t="inlineStr">
         <is>
           <t>자동 영창</t>
         </is>
       </c>
-      <c r="C57" s="30" t="inlineStr">
+      <c r="C58" s="30" t="inlineStr">
         <is>
           <t>화염구 외 주문(불꽃 작렬·메테오·마력 폭주·불장판)도 최적의 순간에 자동 시전합니다. 없으면 이 주문들은 직접 눌러야 합니다.</t>
         </is>
       </c>
-      <c r="D57" s="30" t="inlineStr">
+      <c r="D58" s="30" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="26" customHeight="1" s="13">
-      <c r="A60" s="22" t="inlineStr">
+    <row r="61" ht="26" customHeight="1" s="13">
+      <c r="A61" s="22" t="inlineStr">
         <is>
           <t>6. 스탯 (stats) 컬럼 가이드</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1" s="13">
-      <c r="A61" s="23" t="inlineStr">
+    <row r="62" ht="20" customHeight="1" s="13">
+      <c r="A62" s="23" t="inlineStr">
         <is>
           <t>카드 습득 시 런(Run) 동안 누적되는 스탯입니다. 모든 값은 정수 퍼센트로 입력하며, 대가형 카드는 음수로 손해를 표현합니다.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1" s="13">
-      <c r="A62" s="24" t="inlineStr">
+    <row r="63" ht="24" customHeight="1" s="13">
+      <c r="A63" s="24" t="inlineStr">
         <is>
           <t>열 이름</t>
         </is>
       </c>
-      <c r="B62" s="24" t="inlineStr">
+      <c r="B63" s="24" t="inlineStr">
         <is>
           <t>스탯 키</t>
         </is>
       </c>
-      <c r="C62" s="24" t="inlineStr">
+      <c r="C63" s="24" t="inlineStr">
         <is>
           <t>단위 및 계산 방식</t>
         </is>
       </c>
-      <c r="D62" s="24" t="inlineStr">
+      <c r="D63" s="24" t="inlineStr">
         <is>
           <t>인게임 효과</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="22" customHeight="1" s="13">
-      <c r="A63" s="25" t="inlineStr">
+    <row r="64" ht="22" customHeight="1" s="13">
+      <c r="A64" s="25" t="inlineStr">
         <is>
           <t>주문력%(spPct)</t>
         </is>
       </c>
-      <c r="B63" s="26" t="inlineStr">
+      <c r="B64" s="26" t="inlineStr">
         <is>
           <t>spPct</t>
         </is>
       </c>
-      <c r="C63" s="27" t="inlineStr">
+      <c r="C64" s="27" t="inlineStr">
         <is>
           <t>% (예: 15 = +15%)</t>
         </is>
       </c>
-      <c r="D63" s="27" t="inlineStr">
+      <c r="D64" s="27" t="inlineStr">
         <is>
           <t>기본 주문력 100에 곱해져 모든 피해량이 증가</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="22" customHeight="1" s="13">
-      <c r="A64" s="28" t="inlineStr">
+    <row r="65" ht="22" customHeight="1" s="13">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>가속%(haste)</t>
         </is>
       </c>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="B65" s="29" t="inlineStr">
         <is>
           <t>haste</t>
         </is>
       </c>
-      <c r="C64" s="30" t="inlineStr">
+      <c r="C65" s="30" t="inlineStr">
         <is>
           <t>% (예: 20 = +20%)</t>
         </is>
       </c>
-      <c r="D64" s="30" t="inlineStr">
+      <c r="D65" s="30" t="inlineStr">
         <is>
           <t>시전 바 진행 속도·소환수 공격 주기·불꽃 작렬 충전 속도 증가</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="22" customHeight="1" s="13">
-      <c r="A65" s="25" t="inlineStr">
+    <row r="66" ht="22" customHeight="1" s="13">
+      <c r="A66" s="25" t="inlineStr">
         <is>
           <t>치명타%(crit)</t>
         </is>
       </c>
-      <c r="B65" s="26" t="inlineStr">
+      <c r="B66" s="26" t="inlineStr">
         <is>
           <t>crit</t>
         </is>
       </c>
-      <c r="C65" s="27" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>%p (예: 10 = +10%, 기본 5%)</t>
         </is>
       </c>
-      <c r="D65" s="27" t="inlineStr">
+      <c r="D66" s="27" t="inlineStr">
         <is>
           <t>모든 공격의 치명타 확률 증가 (몰열 2연속 발동에 핵심 기여)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1" s="13">
-      <c r="A66" s="28" t="inlineStr">
+    <row r="67" ht="22" customHeight="1" s="13">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>치명피해%(critDmg)</t>
         </is>
       </c>
-      <c r="B66" s="29" t="inlineStr">
+      <c r="B67" s="29" t="inlineStr">
         <is>
           <t>critDmg</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>% (예: 35 = +35%)</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>치명타 발생 시 기본 150% 피해 배율에 가산</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1" s="13">
-      <c r="A67" s="25" t="inlineStr">
+    <row r="68" ht="22" customHeight="1" s="13">
+      <c r="A68" s="25" t="inlineStr">
         <is>
           <t>지속피해%(burnPct)</t>
         </is>
       </c>
-      <c r="B67" s="26" t="inlineStr">
+      <c r="B68" s="26" t="inlineStr">
         <is>
           <t>burnPct</t>
         </is>
       </c>
-      <c r="C67" s="27" t="inlineStr">
+      <c r="C68" s="27" t="inlineStr">
         <is>
           <t>% (예: 45 = +45%)</t>
         </is>
       </c>
-      <c r="D67" s="27" t="inlineStr">
+      <c r="D68" s="27" t="inlineStr">
         <is>
           <t>화상·메테오 연소·불장판 지속 피해 증가</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="22" customHeight="1" s="13">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69" ht="22" customHeight="1" s="13">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>소환수%(spiritPct)</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B69" s="29" t="inlineStr">
         <is>
           <t>spiritPct</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>% (예: 40 = +40%)</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>화염 정령·불사조 피해 증가</t>
         </is>
@@ -3701,17 +3722,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A34:D34"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>시전 중에도 즉시 발사되는 &lt;b&gt;100% 확정 치명타 보조 마법 [불꽃 작렬]&lt;/b&gt;을 습득합니다.</t>
+          <t>시전 중에도 즉시 발사되는 &lt;b&gt;100% 확정 치명타 보조 마법 [불꽃 작렬]&lt;/b&gt;을 습득합니다. 화염구 치명타 직후에 쓰면 치명타 2연속이 됩니다.</t>
         </is>
       </c>
       <c r="H7" s="19" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>Learn &lt;b&gt;[Fire Blast], an instant spell that always crits&lt;/b&gt; and fires even while casting.</t>
+          <t>Learn &lt;b&gt;[Fire Blast], an instant spell that always crits&lt;/b&gt; and fires even while casting. Use it right after a Fireball crit for 2 crits in a row.</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>하늘에서 거대 운석을 낙하시킵니다. 치명타 2연속(몰열) 시 &lt;b&gt;즉시 노코스트로 투하&lt;/b&gt;됩니다.</t>
+          <t>거대 운석을 떨어뜨립니다. &lt;b&gt;치명타 2연속&lt;/b&gt;이면 메테오가 &lt;b&gt;즉시·무료&lt;/b&gt;로 떨어집니다. 불꽃 작렬은 항상 치명타입니다.</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
-          <t>Call down a giant meteor. After 2 crits in a row (Heating Up), it &lt;b&gt;drops instantly at no cost&lt;/b&gt;.</t>
+          <t>Call down a giant meteor. Land &lt;b&gt;2 crits in a row&lt;/b&gt; and Meteor drops &lt;b&gt;instantly, for free&lt;/b&gt;. Fire Blast always crits.</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr"/>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -1462,7 +1462,7 @@
       <c r="O10" s="20" t="inlineStr"/>
       <c r="P10" s="19" t="inlineStr">
         <is>
-          <t>crit_after_15</t>
+          <t>crit_15_or_combustion</t>
         </is>
       </c>
       <c r="Q10" s="19" t="inlineStr"/>
@@ -2648,8 +2648,8 @@
     <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 값" error="목록(rapid, crit, summon, burn, utility)에서 선택해주세요." promptTitle="[빌드(build) 분류 안내]" prompt="• rapid: 속사 머신건&#10;• crit: 극치명 누킹&#10;• summon: 정령 군단&#10;• burn: 연소 지대&#10;• utility: 유틸리티" type="list">
       <formula1>"rapid,crit,summon,burn,utility"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(has_summon, has_meteor, has_combustion, has_flame_patch, has_any_spell, crit_after_15)에서 선택하거나 빈칸으로 두세요." promptTitle="[선행조건(prerequisite) 안내]" prompt="조건을 달성해야 3지선다에 등장합니다.&#10;빈칸이면 조건 없이 항상 등장합니다." type="list">
-      <formula1>"has_summon,has_meteor,has_combustion,has_flame_patch,has_any_spell,crit_after_15"</formula1>
+    <dataValidation sqref="P2:P100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(has_summon, has_meteor, has_combustion, has_flame_patch, has_any_spell, crit_15_or_combustion)에서 선택하거나 빈칸으로 두세요." promptTitle="[선행조건(prerequisite) 안내]" prompt="조건을 달성해야 3지선다에 등장합니다.&#10;빈칸이면 조건 없이 항상 등장합니다." type="list">
+      <formula1>"has_summon,has_meteor,has_combustion,has_flame_patch,has_any_spell,crit_15_or_combustion"</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(fireblast, meteor, combustion, flame_patch)에서 선택하거나 빈칸으로 두세요." promptTitle="[해금스킬(spellKey) 안내]" prompt="• fireblast: 불꽃 작렬&#10;• meteor: 메테오&#10;• combustion: 마력 폭주&#10;• flame_patch: 불장판" type="list">
       <formula1>"fireblast,meteor,combustion,flame_patch"</formula1>
@@ -3069,17 +3069,17 @@
     <row r="30" ht="22" customHeight="1" s="13">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>crit_after_15</t>
+          <t>crit_15_or_combustion</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>카드를 받은 뒤에도 치명타 확률 15% 이상</t>
+          <t>카드를 받은 뒤에도 치명타 확률 15% 이상, 또는 마력 폭주 습득 시</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>기본 치명타 5%에서 '무모한 일격'(-8%)을 골라 치명타가 0%가 되는 함정 방지</t>
+          <t>기본 치명타 5%에서 '무모한 일격'(-8%)을 골라 치명타가 0%가 되는 함정 방지. 마력 폭주(치명타 100%)가 있으면 치명타 피해 증가가 살아나므로 허용</t>
         </is>
       </c>
     </row>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -522,6 +522,13 @@
 (예: {"charges": 3, "damageBonus": 1.5})</t>
       </text>
     </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>이 카드와 서로 조건을 채우거나 효과를 키우는 카드 ID를 쉼표로 적습니다.
+도감의 연계 표시와 각성 카드 위 '보유 카드와 연계' 표시에 쓰입니다.
+한쪽에만 적어도 게임이 양방향으로 연결합니다. (예: spell_meteor, crit_focus)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -815,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="13" customWidth="1" style="13" min="1" max="1"/>
@@ -837,6 +844,7 @@
     <col width="13" customWidth="1" style="13" min="17" max="17"/>
     <col width="13" customWidth="1" style="13" min="18" max="18"/>
     <col width="13" customWidth="1" style="13" min="19" max="19"/>
+    <col width="13" customWidth="1" style="13" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="13">
@@ -933,6 +941,11 @@
       <c r="S1" s="18" t="inlineStr">
         <is>
           <t>기믹파라미터(JSON)</t>
+        </is>
+      </c>
+      <c r="T1" s="18" t="inlineStr">
+        <is>
+          <t>연계 카드(links)</t>
         </is>
       </c>
     </row>
@@ -992,6 +1005,11 @@
       <c r="Q2" s="19" t="inlineStr"/>
       <c r="R2" s="19" t="inlineStr"/>
       <c r="S2" s="19" t="inlineStr"/>
+      <c r="T2" s="19" t="inlineStr">
+        <is>
+          <t>rapid_split, sum_volley, util_glass_cannon</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" s="13">
       <c r="A3" s="19" t="inlineStr">
@@ -1051,6 +1069,11 @@
         </is>
       </c>
       <c r="S3" s="19" t="inlineStr"/>
+      <c r="T3" s="19" t="inlineStr">
+        <is>
+          <t>rapid_spark, rapid_quickdraw, rapid_gatling, crit_focus</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" s="13">
       <c r="A4" s="19" t="inlineStr">
@@ -1110,6 +1133,11 @@
       <c r="Q4" s="19" t="inlineStr"/>
       <c r="R4" s="19" t="inlineStr"/>
       <c r="S4" s="19" t="inlineStr"/>
+      <c r="T4" s="19" t="inlineStr">
+        <is>
+          <t>util_glass_cannon</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1" s="13">
       <c r="A5" s="19" t="inlineStr">
@@ -1173,6 +1201,11 @@
           <t>{"charges": 4}</t>
         </is>
       </c>
+      <c r="T5" s="19" t="inlineStr">
+        <is>
+          <t>rapid_split</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" s="13">
       <c r="A6" s="19" t="inlineStr">
@@ -1232,6 +1265,11 @@
         </is>
       </c>
       <c r="S6" s="19" t="inlineStr"/>
+      <c r="T6" s="19" t="inlineStr">
+        <is>
+          <t>rapid_split, sum_volley</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="13">
       <c r="A7" s="19" t="inlineStr">
@@ -1291,6 +1329,11 @@
       </c>
       <c r="R7" s="19" t="inlineStr"/>
       <c r="S7" s="19" t="inlineStr"/>
+      <c r="T7" s="19" t="inlineStr">
+        <is>
+          <t>crit_heat, spell_meteor, util_auto_grimoire</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="13">
       <c r="A8" s="19" t="inlineStr">
@@ -1348,6 +1391,11 @@
       <c r="Q8" s="19" t="inlineStr"/>
       <c r="R8" s="19" t="inlineStr"/>
       <c r="S8" s="19" t="inlineStr"/>
+      <c r="T8" s="19" t="inlineStr">
+        <is>
+          <t>rapid_split, crit_heat, crit_reckless, spell_meteor, burn_wildfire</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="13">
       <c r="A9" s="19" t="inlineStr">
@@ -1405,6 +1453,11 @@
       <c r="Q9" s="19" t="inlineStr"/>
       <c r="R9" s="19" t="inlineStr"/>
       <c r="S9" s="19" t="inlineStr"/>
+      <c r="T9" s="19" t="inlineStr">
+        <is>
+          <t>spell_fireblast, crit_focus, spell_combustion, burn_wildfire</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="13">
       <c r="A10" s="19" t="inlineStr">
@@ -1468,6 +1521,11 @@
       <c r="Q10" s="19" t="inlineStr"/>
       <c r="R10" s="19" t="inlineStr"/>
       <c r="S10" s="19" t="inlineStr"/>
+      <c r="T10" s="19" t="inlineStr">
+        <is>
+          <t>crit_focus, spell_combustion</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1" s="13">
       <c r="A11" s="19" t="inlineStr">
@@ -1527,6 +1585,11 @@
       </c>
       <c r="R11" s="19" t="inlineStr"/>
       <c r="S11" s="19" t="inlineStr"/>
+      <c r="T11" s="19" t="inlineStr">
+        <is>
+          <t>spell_fireblast, crit_focus, crit_meteor_storm, crit_meteor_charge, burn_ignite, util_phoenix_reborn, util_auto_grimoire</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1" s="13">
       <c r="A12" s="19" t="inlineStr">
@@ -1590,6 +1653,11 @@
         </is>
       </c>
       <c r="S12" s="19" t="inlineStr"/>
+      <c r="T12" s="19" t="inlineStr">
+        <is>
+          <t>spell_meteor</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="13">
       <c r="A13" s="19" t="inlineStr">
@@ -1655,6 +1723,11 @@
       <c r="S13" s="19" t="inlineStr">
         <is>
           <t>{"charges": 3, "damageBonus": 1.5}</t>
+        </is>
+      </c>
+      <c r="T13" s="19" t="inlineStr">
+        <is>
+          <t>spell_meteor</t>
         </is>
       </c>
     </row>
@@ -1716,6 +1789,11 @@
       </c>
       <c r="R14" s="19" t="inlineStr"/>
       <c r="S14" s="19" t="inlineStr"/>
+      <c r="T14" s="19" t="inlineStr">
+        <is>
+          <t>crit_heat, crit_reckless, crit_crimson_frenzy, util_phoenix_reborn, util_auto_grimoire</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="13">
       <c r="A15" s="19" t="inlineStr">
@@ -1779,6 +1857,11 @@
         </is>
       </c>
       <c r="S15" s="19" t="inlineStr"/>
+      <c r="T15" s="19" t="inlineStr">
+        <is>
+          <t>spell_combustion</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="13">
       <c r="A16" s="19" t="inlineStr">
@@ -1838,6 +1921,11 @@
         </is>
       </c>
       <c r="S16" s="19" t="inlineStr"/>
+      <c r="T16" s="19" t="inlineStr">
+        <is>
+          <t>sum_fury, sum_volley, sum_pact, sum_cinder_lord</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="13">
       <c r="A17" s="19" t="inlineStr">
@@ -1899,6 +1987,11 @@
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="19" t="inlineStr"/>
       <c r="S17" s="19" t="inlineStr"/>
+      <c r="T17" s="19" t="inlineStr">
+        <is>
+          <t>sum_spirit</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="13">
       <c r="A18" s="19" t="inlineStr">
@@ -1962,6 +2055,11 @@
         </is>
       </c>
       <c r="S18" s="19" t="inlineStr"/>
+      <c r="T18" s="19" t="inlineStr">
+        <is>
+          <t>rapid_spark, rapid_gatling, sum_spirit</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="13">
       <c r="A19" s="19" t="inlineStr">
@@ -2025,6 +2123,11 @@
       <c r="Q19" s="19" t="inlineStr"/>
       <c r="R19" s="19" t="inlineStr"/>
       <c r="S19" s="19" t="inlineStr"/>
+      <c r="T19" s="19" t="inlineStr">
+        <is>
+          <t>sum_spirit, sum_cinder_lord</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="13">
       <c r="A20" s="19" t="inlineStr">
@@ -2088,6 +2191,11 @@
         </is>
       </c>
       <c r="S20" s="19" t="inlineStr"/>
+      <c r="T20" s="19" t="inlineStr">
+        <is>
+          <t>sum_spirit, sum_pact</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="13">
       <c r="A21" s="19" t="inlineStr">
@@ -2145,6 +2253,11 @@
       <c r="Q21" s="19" t="inlineStr"/>
       <c r="R21" s="19" t="inlineStr"/>
       <c r="S21" s="19" t="inlineStr"/>
+      <c r="T21" s="19" t="inlineStr">
+        <is>
+          <t>spell_meteor, spell_flame_patch, burn_wildfire</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="13">
       <c r="A22" s="19" t="inlineStr">
@@ -2204,6 +2317,11 @@
       </c>
       <c r="R22" s="19" t="inlineStr"/>
       <c r="S22" s="19" t="inlineStr"/>
+      <c r="T22" s="19" t="inlineStr">
+        <is>
+          <t>burn_ignite, burn_spread, util_phoenix_reborn, util_auto_grimoire</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1" s="13">
       <c r="A23" s="19" t="inlineStr">
@@ -2269,6 +2387,11 @@
       <c r="S23" s="19" t="inlineStr">
         <is>
           <t>{"cooldownMult": 0.7, "damageBonus": 0.5}</t>
+        </is>
+      </c>
+      <c r="T23" s="19" t="inlineStr">
+        <is>
+          <t>spell_flame_patch</t>
         </is>
       </c>
     </row>
@@ -2334,6 +2457,11 @@
           <t>{"igniteRatioMult": 6, "igniteOnAllHits": true, "igniteCarryOver": true}</t>
         </is>
       </c>
+      <c r="T24" s="19" t="inlineStr">
+        <is>
+          <t>crit_focus, crit_heat, burn_ignite</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1" s="13">
       <c r="A25" s="19" t="inlineStr">
@@ -2391,6 +2519,11 @@
       <c r="Q25" s="19" t="inlineStr"/>
       <c r="R25" s="19" t="inlineStr"/>
       <c r="S25" s="19" t="inlineStr"/>
+      <c r="T25" s="19" t="inlineStr">
+        <is>
+          <t>util_executioner</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1" s="13">
       <c r="A26" s="19" t="inlineStr">
@@ -2454,6 +2587,11 @@
           <t>{"executionerMult": 0.7}</t>
         </is>
       </c>
+      <c r="T26" s="19" t="inlineStr">
+        <is>
+          <t>util_power</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="13">
       <c r="A27" s="19" t="inlineStr">
@@ -2513,6 +2651,11 @@
       <c r="Q27" s="19" t="inlineStr"/>
       <c r="R27" s="19" t="inlineStr"/>
       <c r="S27" s="19" t="inlineStr"/>
+      <c r="T27" s="19" t="inlineStr">
+        <is>
+          <t>rapid_spark, rapid_overload</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="13">
       <c r="A28" s="19" t="inlineStr">
@@ -2576,6 +2719,11 @@
         </is>
       </c>
       <c r="S28" s="19" t="inlineStr"/>
+      <c r="T28" s="19" t="inlineStr">
+        <is>
+          <t>spell_meteor, spell_combustion, spell_flame_patch</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="13">
       <c r="A29" s="19" t="inlineStr">
@@ -2639,6 +2787,11 @@
         </is>
       </c>
       <c r="S29" s="19" t="inlineStr"/>
+      <c r="T29" s="19" t="inlineStr">
+        <is>
+          <t>spell_fireblast, spell_meteor, spell_combustion, spell_flame_patch</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="5">

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -431,17 +431,20 @@
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>카드의 빌드 분류 태그 (드롭다운 제공):
+- spell: 📜 고대 주문서 (빌드가 갈라지는 축)
+- crit: 🎯 극치명 누킹 (열기·메테오)
+- combustion: ☀️ 폭주 극딜 (업화 2단계에 열림)
 - rapid: ⚡ 속사 머신건
-- crit: 🎯 극치명 누킹
 - summon: 🔥 정령 군단
-- burn: 🌋 연소 지대
-- utility: ✨ 유틸리티</t>
+- burn: ♨️ 화상 확산
+- utility: ✨ 유틸리티
+주문서·유틸리티는 주력 빌드 판정에서 빠집니다.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>한 런(Run)에서 최대로 습득 가능한 횟수입니다.
-이 횟수만큼 습득하면 이후 3지선다 추첨 풀에서 자동 제외됩니다. (보통 1~5)</t>
+이 횟수만큼 습득하면 이후 3지선다 추첨 풀에서 자동 제외됩니다. (수치 카드 3, 나머지 1~4)</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
@@ -525,7 +528,7 @@
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>이 카드와 서로 조건을 채우거나 효과를 키우는 카드 ID를 쉼표로 적습니다.
-도감의 연계 표시와 각성 카드 위 '보유 카드와 연계' 표시에 쓰입니다.
+도감에서 카드를 눌렀을 때 밝아지는 연계 카드로 쓰입니다(각성 카드 창에는 표시하지 않음).
 한쪽에만 적어도 게임이 양방향으로 연결합니다. (예: spell_meteor, crit_focus)</t>
       </text>
     </comment>
@@ -976,11 +979,11 @@
         </is>
       </c>
       <c r="F2" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2" s="19" t="inlineStr">
         <is>
-          <t>화염 마법 시전 속도가 &lt;b&gt;+20%&lt;/b&gt; 빨라집니다.</t>
+          <t>화염 마법 시전 속도가 &lt;b&gt;+30%&lt;/b&gt; 빨라집니다.</t>
         </is>
       </c>
       <c r="H2" s="19" t="inlineStr">
@@ -990,12 +993,12 @@
       </c>
       <c r="I2" s="19" t="inlineStr">
         <is>
-          <t>Fire spell cast speed &lt;b&gt;+20%&lt;/b&gt;.</t>
+          <t>Fire spell cast speed &lt;b&gt;+30%&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J2" s="20" t="inlineStr"/>
       <c r="K2" s="20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L2" s="20" t="inlineStr"/>
       <c r="M2" s="20" t="inlineStr"/>
@@ -1294,7 +1297,7 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>crit</t>
+          <t>spell</t>
         </is>
       </c>
       <c r="F7" s="20" t="n">
@@ -1362,11 +1365,11 @@
         </is>
       </c>
       <c r="F8" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>치명타 확률이 &lt;b&gt;+10%&lt;/b&gt; 증가합니다.</t>
+          <t>치명타 확률이 &lt;b&gt;+15%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
@@ -1376,13 +1379,13 @@
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>Critical strike chance &lt;b&gt;+10%&lt;/b&gt;.</t>
+          <t>Critical strike chance &lt;b&gt;+15%&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr"/>
       <c r="K8" s="20" t="inlineStr"/>
       <c r="L8" s="20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M8" s="20" t="inlineStr"/>
       <c r="N8" s="20" t="inlineStr"/>
@@ -1424,11 +1427,11 @@
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>치명타 피해량이 &lt;b&gt;+35%&lt;/b&gt; 증가합니다.</t>
+          <t>치명타 피해량이 &lt;b&gt;+50%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
@@ -1438,14 +1441,14 @@
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>Critical damage &lt;b&gt;+35%&lt;/b&gt;.</t>
+          <t>Critical damage &lt;b&gt;+50%&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr"/>
       <c r="K9" s="20" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr"/>
       <c r="M9" s="20" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="N9" s="20" t="inlineStr"/>
       <c r="O9" s="20" t="inlineStr"/>
@@ -1482,7 +1485,7 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>crit</t>
+          <t>combustion</t>
         </is>
       </c>
       <c r="F10" s="20" t="n">
@@ -1550,7 +1553,7 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>crit</t>
+          <t>spell</t>
         </is>
       </c>
       <c r="F11" s="20" t="n">
@@ -1754,7 +1757,7 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>crit</t>
+          <t>spell</t>
         </is>
       </c>
       <c r="F14" s="20" t="n">
@@ -1818,7 +1821,7 @@
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>crit</t>
+          <t>combustion</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
@@ -1954,11 +1957,11 @@
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>정령·불사조 등 &lt;b&gt;소환수 피해량이 +40%&lt;/b&gt; 증가합니다.</t>
+          <t>정령·불사조 등 &lt;b&gt;소환수 피해량이 +60%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr">
@@ -1968,7 +1971,7 @@
       </c>
       <c r="I17" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Summon damage +40%&lt;/b&gt; (Fire Spirits, Phoenix).</t>
+          <t>&lt;b&gt;Summon damage +60%&lt;/b&gt; (Fire Spirits, Phoenix).</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr"/>
@@ -1977,7 +1980,7 @@
       <c r="M17" s="20" t="inlineStr"/>
       <c r="N17" s="20" t="inlineStr"/>
       <c r="O17" s="20" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P17" s="19" t="inlineStr">
         <is>
@@ -2224,11 +2227,11 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>화상·연소·불장판 등 &lt;b&gt;지속 피해량이 +45%&lt;/b&gt; 증가합니다.</t>
+          <t>화상·연소·불장판 등 &lt;b&gt;지속 피해량이 +65%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H21" s="19" t="inlineStr">
@@ -2238,7 +2241,7 @@
       </c>
       <c r="I21" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Damage over time +45%&lt;/b&gt; (Ignite, Meteor burn, Flame Patch).</t>
+          <t>&lt;b&gt;Damage over time +65%&lt;/b&gt; (Ignite, Meteor burn, Flame Patch).</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr"/>
@@ -2246,7 +2249,7 @@
       <c r="L21" s="20" t="inlineStr"/>
       <c r="M21" s="20" t="inlineStr"/>
       <c r="N21" s="20" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="O21" s="20" t="inlineStr"/>
       <c r="P21" s="19" t="inlineStr"/>
@@ -2282,7 +2285,7 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>burn</t>
+          <t>spell</t>
         </is>
       </c>
       <c r="F22" s="20" t="n">
@@ -2490,11 +2493,11 @@
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>주문력이 &lt;b&gt;+15%&lt;/b&gt; 증가합니다.</t>
+          <t>주문력이 &lt;b&gt;+22%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
@@ -2504,11 +2507,11 @@
       </c>
       <c r="I25" s="19" t="inlineStr">
         <is>
-          <t>Spell Power &lt;b&gt;+15%&lt;/b&gt;.</t>
+          <t>Spell Power &lt;b&gt;+22%&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J25" s="20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K25" s="20" t="inlineStr"/>
       <c r="L25" s="20" t="inlineStr"/>
@@ -2798,8 +2801,8 @@
     <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 값" error="목록(common, rare, legendary)에서 선택해주세요." promptTitle="[희귀도(rarity) 옵션 안내]" prompt="• common: 일반&#10;• rare: 희귀&#10;• legendary: 전설 (보스전 우대)" type="list">
       <formula1>"common,rare,legendary"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 값" error="목록(rapid, crit, summon, burn, utility)에서 선택해주세요." promptTitle="[빌드(build) 분류 안내]" prompt="• rapid: 속사 머신건&#10;• crit: 극치명 누킹&#10;• summon: 정령 군단&#10;• burn: 연소 지대&#10;• utility: 유틸리티" type="list">
-      <formula1>"rapid,crit,summon,burn,utility"</formula1>
+    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" errorTitle="유효하지 않은 값" error="목록(spell, crit, combustion, rapid, summon, burn, utility)에서 선택해주세요." promptTitle="[빌드(build) 분류 안내]" prompt="• rapid: 속사 머신건&#10;• crit: 극치명 누킹&#10;• summon: 정령 군단&#10;• burn: 연소 지대&#10;• utility: 유틸리티" type="list">
+      <formula1>"spell,crit,combustion,rapid,summon,burn,utility"</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(has_summon, has_meteor, has_combustion, has_flame_patch, has_any_spell, crit_15_or_combustion)에서 선택하거나 빈칸으로 두세요." promptTitle="[선행조건(prerequisite) 안내]" prompt="조건을 달성해야 3지선다에 등장합니다.&#10;빈칸이면 조건 없이 항상 등장합니다." type="list">
       <formula1>"has_summon,has_meteor,has_combustion,has_flame_patch,has_any_spell,crit_15_or_combustion"</formula1>
@@ -2822,7 +2825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="13" min="1" max="1"/>
@@ -2950,7 +2953,7 @@
     <row r="12" ht="20" customHeight="1" s="13">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>카드가 지향하는 전투 플레이스타일 태그입니다. 각성 카드에 빌드 배지로 표시됩니다.</t>
+          <t>카드가 지향하는 전투 플레이스타일 태그입니다. 각성 카드에 빌드 배지로, 도감에 탭으로 표시됩니다. 주문서·유틸리티를 뺀 빌드 중 가장 많이 가진 빌드(2장 이상)가 주력 빌드가 되어 추첨에서 우대받습니다.</t>
         </is>
       </c>
     </row>
@@ -2979,22 +2982,22 @@
     <row r="14" ht="22" customHeight="1" s="13">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>rapid</t>
+          <t>spell</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>⚡ 속사 머신건</t>
+          <t>📜 고대 주문서</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>화염구 난사 및 시전 가속</t>
+          <t>빌드가 갈라지는 축 (주력 빌드 판정 제외)</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>가속, 분열 화염구, 속사 장전(충전형), 과부하 시전(대가형), 화염 기관총</t>
+          <t>불꽃 작렬, 메테오, 마력 폭주, 불장판</t>
         </is>
       </c>
     </row>
@@ -3016,466 +3019,466 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>치명타·치명 피해, 무모한 일격(대가형), 잠열 충전(충전형), 메테오·마력 폭주</t>
+          <t>치명타·치명 피해, 태양석 메테오, 잠열 충전(충전형)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" s="13">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>combustion</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>🔥 정령 군단</t>
+          <t>☀️ 폭주 극딜</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>화염 정령 소환 및 협공</t>
+          <t>마력 폭주 5초에 몰아치기 (업화 2단계에 열림)</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>정령 소환, 정령의 분노, 정령 계약(대가형), 일제 협공, 잿더미 군단장</t>
+          <t>무모한 일격(대가형), 진홍의 마력 폭주</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" s="13">
       <c r="A17" s="28" t="inlineStr">
         <is>
-          <t>burn</t>
+          <t>rapid</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>🌋 연소 지대</t>
+          <t>⚡ 속사 머신건</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>화상·불장판 지속 피해</t>
+          <t>화염구 난사 및 시전 가속</t>
         </is>
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>지속 피해 강화, 불장판, 번지는 불길, 들불</t>
+          <t>가속, 분열 화염구, 속사 장전(충전형), 과부하 시전(대가형), 화염 기관총</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" s="13">
       <c r="A18" s="25" t="inlineStr">
         <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>🔥 정령 군단</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>화염 정령 소환 및 협공</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>정령 소환, 정령의 분노, 정령 계약(대가형), 일제 협공, 잿더미 군단장</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="13">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>♨️ 화상 확산</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>화상·불장판 지속 피해</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>지속 피해 강화, 번지는 불길, 들불</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="13">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
           <t>utility</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>✨ 유틸리티</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>범용 강화</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>마력 증폭, 유리 대포(대가형), 처형인, 불사조의 가호</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1" s="13">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>범용 강화 (주력 빌드 판정 제외)</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>마력 증폭, 유리 대포(대가형), 처형인, 불사조의 가호, 자동 영창</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1" s="13">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>3. 선행 조건 필터 (prerequisite) 가이드</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1" s="13">
-      <c r="A22" s="23" t="inlineStr">
+    <row r="24" ht="20" customHeight="1" s="13">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>특정 조건을 만족했을 때만 3지선다 목록에 등장하도록 제어하는 필터입니다. (비어있으면 무조건 등장)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1" s="13">
-      <c r="A23" s="24" t="inlineStr">
+    <row r="25" ht="24" customHeight="1" s="13">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>값 (Enum)</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>등장 조건</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>기획 의도 및 목적</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" s="13">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>(빈칸)</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="inlineStr">
-        <is>
-          <t>조건 없음</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>처음부터 누구나 언제든 획득 가능한 기본 카드</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" s="13">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>has_summon</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>화염 정령 보유 시</t>
-        </is>
-      </c>
-      <c r="C25" s="30" t="inlineStr">
-        <is>
-          <t>정령이 없는데 소환수 강화 카드가 나와 선택지를 낭비하는 현상 방지</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" s="13">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>has_meteor</t>
+          <t>(빈칸)</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>메테오 습득 시</t>
+          <t>조건 없음</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>메테오를 배우지 않은 상태에서 메테오 강화 카드가 뜨는 현상 방지</t>
+          <t>처음부터 누구나 언제든 획득 가능한 기본 카드</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" s="13">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>has_combustion</t>
+          <t>has_summon</t>
         </is>
       </c>
       <c r="B27" s="29" t="inlineStr">
         <is>
-          <t>마력 폭주 습득 시</t>
+          <t>화염 정령 보유 시</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>마력 폭주를 배운 상태에서만 '진홍의 마력 폭주'가 등장</t>
+          <t>정령이 없는데 소환수 강화 카드가 나와 선택지를 낭비하는 현상 방지</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" s="13">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>has_flame_patch</t>
+          <t>has_meteor</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>불장판 습득 시</t>
+          <t>메테오 습득 시</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>불장판을 배운 상태에서만 '번지는 불길'이 등장</t>
+          <t>메테오를 배우지 않은 상태에서 메테오 강화 카드가 뜨는 현상 방지</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" s="13">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>has_any_spell</t>
+          <t>has_combustion</t>
         </is>
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>쿨다운 스킬 1개 이상 습득 시</t>
+          <t>마력 폭주 습득 시</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>쿨다운 스킬이 없는데 '쿨다운 초기화' 카드가 떠서 무용지물이 되는 현상 방지</t>
+          <t>마력 폭주를 배운 상태에서만 '진홍의 마력 폭주'가 등장</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" s="13">
       <c r="A30" s="25" t="inlineStr">
         <is>
+          <t>has_flame_patch</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>불장판 습득 시</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>불장판을 배운 상태에서만 '번지는 불길'이 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1" s="13">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>has_any_spell</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>쿨다운 스킬 1개 이상 습득 시</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>쿨다운 스킬이 없는데 '쿨다운 초기화' 카드가 떠서 무용지물이 되는 현상 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1" s="13">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
           <t>crit_15_or_combustion</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>카드를 받은 뒤에도 치명타 확률 15% 이상, 또는 마력 폭주 습득 시</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>기본 치명타 5%에서 '무모한 일격'(-8%)을 골라 치명타가 0%가 되는 함정 방지. 마력 폭주(치명타 100%)가 있으면 치명타 피해 증가가 살아나므로 허용</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1" s="13">
-      <c r="A33" s="22" t="inlineStr">
+    <row r="35" ht="26" customHeight="1" s="13">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>4. 고대 주문서 해금 스킬 (spellKey) 가이드</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1" s="13">
-      <c r="A34" s="23" t="inlineStr">
+    <row r="36" ht="20" customHeight="1" s="13">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>주문서 카드를 획득했을 때 즉시 해금해 줄 스킬입니다. 이미 습득한 주문서는 3지선다에 다시 등장하지 않습니다. (자동 시전은 처음부터 기본 제공)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="24" customHeight="1" s="13">
-      <c r="A35" s="24" t="inlineStr">
+    <row r="37" ht="24" customHeight="1" s="13">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>값 (Enum)</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>해금되는 스킬명</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>스킬 유형</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D37" s="24" t="inlineStr">
         <is>
           <t>스킬 효과 요약</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1" s="13">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>fireblast</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="inlineStr">
-        <is>
-          <t>불꽃 작렬</t>
-        </is>
-      </c>
-      <c r="C36" s="27" t="inlineStr">
-        <is>
-          <t>보조 즉발기</t>
-        </is>
-      </c>
-      <c r="D36" s="27" t="inlineStr">
-        <is>
-          <t>시전 중에도 즉시 발사되는 주문력 120% 확정 치명타 (2회 충전, 충전 8초)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1" s="13">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>meteor</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>메테오</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>강타기</t>
-        </is>
-      </c>
-      <c r="D37" s="30" t="inlineStr">
-        <is>
-          <t>주문력 320% 운석 투하 및 6초 연소, 치명타 2연속(몰열) 시 즉시 노코스트 시전</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" s="13">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>combustion</t>
+          <t>fireblast</t>
         </is>
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>마력 폭주</t>
+          <t>불꽃 작렬</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>버프 극딜기</t>
+          <t>보조 즉발기</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
         <is>
-          <t>5초간 모든 마법 치명타 100% 확정 및 시전 속도 +20% (재사용 30초)</t>
+          <t>시전 중에도 즉시 발사되는 주문력 120% 확정 치명타 (2회 충전, 충전 8초)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" s="13">
       <c r="A39" s="28" t="inlineStr">
         <is>
+          <t>meteor</t>
+        </is>
+      </c>
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>메테오</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>강타기</t>
+        </is>
+      </c>
+      <c r="D39" s="30" t="inlineStr">
+        <is>
+          <t>주문력 320% 운석 투하 및 6초 연소, 치명타 2연속(몰열) 시 즉시 노코스트 시전</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1" s="13">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>combustion</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>마력 폭주</t>
+        </is>
+      </c>
+      <c r="C40" s="27" t="inlineStr">
+        <is>
+          <t>버프 극딜기</t>
+        </is>
+      </c>
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>5초간 모든 마법 치명타 100% 확정 및 시전 속도 +20% (재사용 30초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1" s="13">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
           <t>flame_patch</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>불장판</t>
         </is>
       </c>
-      <c r="C39" s="30" t="inlineStr">
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>지속 피해기</t>
         </is>
       </c>
-      <c r="D39" s="30" t="inlineStr">
+      <c r="D41" s="30" t="inlineStr">
         <is>
           <t>몬스터 발밑에 7초간 화염 지대 생성, 0.5초마다 주문력 50% 피해 (재사용 10초)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1" s="13">
-      <c r="A42" s="22" t="inlineStr">
+    <row r="44" ht="26" customHeight="1" s="13">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>5. 특수 고유 메커니즘 (mechanic) 및 파라미터 가이드</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1" s="13">
-      <c r="A43" s="23" t="inlineStr">
+    <row r="45" ht="20" customHeight="1" s="13">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>단순 스탯 증가가 아닌 전투 규칙을 바꾸는 효과입니다. 충전형은 스테이지 시작마다 충전이 다시 채워집니다.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1" s="13">
-      <c r="A44" s="24" t="inlineStr">
+    <row r="46" ht="24" customHeight="1" s="13">
+      <c r="A46" s="24" t="inlineStr">
         <is>
           <t>기믹 키 (mechanic)</t>
         </is>
       </c>
-      <c r="B44" s="24" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
         <is>
           <t>효과 명칭</t>
         </is>
       </c>
-      <c r="C44" s="24" t="inlineStr">
+      <c r="C46" s="24" t="inlineStr">
         <is>
           <t>동작 메커니즘 설명</t>
         </is>
       </c>
-      <c r="D44" s="24" t="inlineStr">
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>기믹 파라미터 예시 (JSON)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1" s="13">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>split_fireball</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>분열 화염구</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>화염구 적중 시 작은 불씨가 분열되어 추가 타격합니다. (스택당 2개, 최대 6개, 각 주문력 40%)</t>
-        </is>
-      </c>
-      <c r="D45" s="27" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1" s="13">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>gatling_mode</t>
-        </is>
-      </c>
-      <c r="B46" s="29" t="inlineStr">
-        <is>
-          <t>화염 기관총</t>
-        </is>
-      </c>
-      <c r="C46" s="30" t="inlineStr">
-        <is>
-          <t>화염구 기본 시전 시간과 공통 대기 시간이 0.3초로 단축됩니다. (최소 0.12초)</t>
-        </is>
-      </c>
-      <c r="D46" s="30" t="inlineStr">
-        <is>
-          <t>없음</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" s="13">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>quickdraw_charge</t>
+          <t>split_fireball</t>
         </is>
       </c>
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>속사 장전 (충전형)</t>
+          <t>분열 화염구</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>스테이지 시작마다 화염구를 시전 없이 즉시 발사하는 충전을 얻습니다. (중첩 시 충전 합산)</t>
+          <t>화염구 적중 시 작은 불씨가 분열되어 추가 타격합니다. (스택당 2개, 최대 6개, 각 주문력 40%)</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
         <is>
-          <t>{"charges": 4}</t>
+          <t>없음</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" s="13">
       <c r="A48" s="28" t="inlineStr">
         <is>
-          <t>meteor_buff</t>
+          <t>gatling_mode</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>태양석 메테오</t>
+          <t>화염 기관총</t>
         </is>
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>메테오를 습득시키고, 스택당 재사용 대기 50% 감소(최소 4초)·피해 +60%가 적용됩니다.</t>
+          <t>화염구 기본 시전 시간과 공통 대기 시간이 0.3초로 단축됩니다. (최소 0.12초)</t>
         </is>
       </c>
       <c r="D48" s="30" t="inlineStr">
@@ -3487,39 +3490,39 @@
     <row r="49" ht="22" customHeight="1" s="13">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>meteor_charge</t>
+          <t>quickdraw_charge</t>
         </is>
       </c>
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>잠열 충전 (충전형)</t>
+          <t>속사 장전 (충전형)</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>스테이지 시작마다 메테오 피해 증폭 충전을 얻습니다. 메테오 발사 시 1회씩 소모됩니다.</t>
+          <t>스테이지 시작마다 화염구를 시전 없이 즉시 발사하는 충전을 얻습니다. (중첩 시 충전 합산)</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
         <is>
-          <t>{"charges": 3, "damageBonus": 1.5}</t>
+          <t>{"charges": 4}</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" s="13">
       <c r="A50" s="28" t="inlineStr">
         <is>
-          <t>combustion_god</t>
+          <t>meteor_buff</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>진홍의 마력 폭주</t>
+          <t>태양석 메테오</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>마력 폭주를 습득시키고, 지속시간 2배·폭주 중 모든 피해 2.5배가 적용됩니다.</t>
+          <t>메테오를 습득시키고, 스택당 재사용 대기 50% 감소(최소 4초)·피해 +60%가 적용됩니다.</t>
         </is>
       </c>
       <c r="D50" s="30" t="inlineStr">
@@ -3531,39 +3534,39 @@
     <row r="51" ht="22" customHeight="1" s="13">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>extra_spirit</t>
+          <t>meteor_charge</t>
         </is>
       </c>
       <c r="B51" s="26" t="inlineStr">
         <is>
-          <t>화염 정령 소환</t>
+          <t>잠열 충전 (충전형)</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>화염 정령을 1기 추가 소환합니다. (최대 4기, 1.3초마다 주문력 45% x 정령 수 피해)</t>
+          <t>스테이지 시작마다 메테오 피해 증폭 충전을 얻습니다. 메테오 발사 시 1회씩 소모됩니다.</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>{"charges": 3, "damageBonus": 1.5}</t>
         </is>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" s="13">
       <c r="A52" s="28" t="inlineStr">
         <is>
-          <t>synchronized_fire</t>
+          <t>combustion_god</t>
         </is>
       </c>
       <c r="B52" s="29" t="inlineStr">
         <is>
-          <t>일제 협공 사격</t>
+          <t>진홍의 마력 폭주</t>
         </is>
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>마법사가 화염구를 발사할 때마다 모든 정령이 동시에 협공합니다.</t>
+          <t>마력 폭주를 습득시키고, 지속시간 2배·폭주 중 모든 피해 2.5배가 적용됩니다.</t>
         </is>
       </c>
       <c r="D52" s="30" t="inlineStr">
@@ -3575,17 +3578,17 @@
     <row r="53" ht="22" customHeight="1" s="13">
       <c r="A53" s="25" t="inlineStr">
         <is>
-          <t>cinder_lord</t>
+          <t>extra_spirit</t>
         </is>
       </c>
       <c r="B53" s="26" t="inlineStr">
         <is>
-          <t>잿더미 군단장</t>
+          <t>화염 정령 소환</t>
         </is>
       </c>
       <c r="C53" s="27" t="inlineStr">
         <is>
-          <t>소환수 1기당 마법사의 모든 주문 피해가 +30% 증폭됩니다.</t>
+          <t>화염 정령을 1기 추가 소환합니다. (최대 4기, 1.3초마다 주문력 45% x 정령 수 피해)</t>
         </is>
       </c>
       <c r="D53" s="27" t="inlineStr">
@@ -3597,276 +3600,320 @@
     <row r="54" ht="22" customHeight="1" s="13">
       <c r="A54" s="28" t="inlineStr">
         <is>
-          <t>patch_boost</t>
+          <t>synchronized_fire</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>번지는 불길</t>
+          <t>일제 협공 사격</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>불장판 재사용 대기시간에 cooldownMult를 곱하고 불장판 피해를 damageBonus만큼 증가시킵니다.</t>
+          <t>마법사가 화염구를 발사할 때마다 모든 정령이 동시에 협공합니다.</t>
         </is>
       </c>
       <c r="D54" s="30" t="inlineStr">
         <is>
-          <t>{"cooldownMult": 0.7, "damageBonus": 0.5}</t>
+          <t>없음</t>
         </is>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" s="13">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>wildfire</t>
+          <t>cinder_lord</t>
         </is>
       </c>
       <c r="B55" s="26" t="inlineStr">
         <is>
-          <t>들불</t>
+          <t>잿더미 군단장</t>
         </is>
       </c>
       <c r="C55" s="27" t="inlineStr">
         <is>
-          <t>모든 적중이 화상(피해의 22%)을 남기고, 치명타 화상은 igniteRatioMult배로 키웁니다. igniteCarryOver면 쓰러진 적의 남은 화상이 다음 적에게 이어집니다.</t>
+          <t>소환수 1기당 마법사의 모든 주문 피해가 +30% 증폭됩니다.</t>
         </is>
       </c>
       <c r="D55" s="27" t="inlineStr">
         <is>
-          <t>{"igniteRatioMult": 6, "igniteOnAllHits": true, "igniteCarryOver": true}</t>
+          <t>없음</t>
         </is>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" s="13">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>executioner</t>
+          <t>patch_boost</t>
         </is>
       </c>
       <c r="B56" s="29" t="inlineStr">
         <is>
-          <t>처형인의 불꽃</t>
+          <t>번지는 불길</t>
         </is>
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>적 체력이 40% 이하일 때 모든 피해량이 executionerMult만큼 증가합니다. (스택 시 합산)</t>
+          <t>불장판 재사용 대기시간에 cooldownMult를 곱하고 불장판 피해를 damageBonus만큼 증가시킵니다.</t>
         </is>
       </c>
       <c r="D56" s="30" t="inlineStr">
         <is>
-          <t>{"executionerMult": 0.7}</t>
+          <t>{"cooldownMult": 0.7, "damageBonus": 0.5}</t>
         </is>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" s="13">
       <c r="A57" s="25" t="inlineStr">
         <is>
-          <t>phoenix_reset</t>
+          <t>wildfire</t>
         </is>
       </c>
       <c r="B57" s="26" t="inlineStr">
         <is>
-          <t>불사조의 가호</t>
+          <t>들불</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
         <is>
-          <t>불사조가 2.4초마다 확정 치명타로 협공하고, 치명타 적중 시 10% 확률로 모든 스킬의 재사용 대기가 초기화됩니다.</t>
+          <t>모든 적중이 화상(피해의 22%)을 남기고, 치명타 화상은 igniteRatioMult배로 키웁니다. igniteCarryOver면 쓰러진 적의 남은 화상이 다음 적에게 이어집니다.</t>
         </is>
       </c>
       <c r="D57" s="27" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>{"igniteRatioMult": 6, "igniteOnAllHits": true, "igniteCarryOver": true}</t>
         </is>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" s="13">
       <c r="A58" s="28" t="inlineStr">
         <is>
+          <t>executioner</t>
+        </is>
+      </c>
+      <c r="B58" s="29" t="inlineStr">
+        <is>
+          <t>처형인의 불꽃</t>
+        </is>
+      </c>
+      <c r="C58" s="30" t="inlineStr">
+        <is>
+          <t>적 체력이 40% 이하일 때 모든 피해량이 executionerMult만큼 증가합니다. (스택 시 합산)</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="inlineStr">
+        <is>
+          <t>{"executionerMult": 0.7}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1" s="13">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>phoenix_reset</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>불사조의 가호</t>
+        </is>
+      </c>
+      <c r="C59" s="27" t="inlineStr">
+        <is>
+          <t>불사조가 2.4초마다 확정 치명타로 협공하고, 치명타 적중 시 10% 확률로 모든 스킬의 재사용 대기가 초기화됩니다.</t>
+        </is>
+      </c>
+      <c r="D59" s="27" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1" s="13">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
           <t>smart_autocast</t>
         </is>
       </c>
-      <c r="B58" s="29" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>자동 영창</t>
         </is>
       </c>
-      <c r="C58" s="30" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>화염구 외 주문(불꽃 작렬·메테오·마력 폭주·불장판)도 최적의 순간에 자동 시전합니다. 없으면 이 주문들은 직접 눌러야 합니다.</t>
         </is>
       </c>
-      <c r="D58" s="30" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="26" customHeight="1" s="13">
-      <c r="A61" s="22" t="inlineStr">
+    <row r="63" ht="26" customHeight="1" s="13">
+      <c r="A63" s="22" t="inlineStr">
         <is>
           <t>6. 스탯 (stats) 컬럼 가이드</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1" s="13">
-      <c r="A62" s="23" t="inlineStr">
+    <row r="64" ht="20" customHeight="1" s="13">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>카드 습득 시 런(Run) 동안 누적되는 스탯입니다. 모든 값은 정수 퍼센트로 입력하며, 대가형 카드는 음수로 손해를 표현합니다.</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="24" customHeight="1" s="13">
-      <c r="A63" s="24" t="inlineStr">
+    <row r="65" ht="24" customHeight="1" s="13">
+      <c r="A65" s="24" t="inlineStr">
         <is>
           <t>열 이름</t>
         </is>
       </c>
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B65" s="24" t="inlineStr">
         <is>
           <t>스탯 키</t>
         </is>
       </c>
-      <c r="C63" s="24" t="inlineStr">
+      <c r="C65" s="24" t="inlineStr">
         <is>
           <t>단위 및 계산 방식</t>
         </is>
       </c>
-      <c r="D63" s="24" t="inlineStr">
+      <c r="D65" s="24" t="inlineStr">
         <is>
           <t>인게임 효과</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1" s="13">
-      <c r="A64" s="25" t="inlineStr">
-        <is>
-          <t>주문력%(spPct)</t>
-        </is>
-      </c>
-      <c r="B64" s="26" t="inlineStr">
-        <is>
-          <t>spPct</t>
-        </is>
-      </c>
-      <c r="C64" s="27" t="inlineStr">
-        <is>
-          <t>% (예: 15 = +15%)</t>
-        </is>
-      </c>
-      <c r="D64" s="27" t="inlineStr">
-        <is>
-          <t>기본 주문력 100에 곱해져 모든 피해량이 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1" s="13">
-      <c r="A65" s="28" t="inlineStr">
-        <is>
-          <t>가속%(haste)</t>
-        </is>
-      </c>
-      <c r="B65" s="29" t="inlineStr">
-        <is>
-          <t>haste</t>
-        </is>
-      </c>
-      <c r="C65" s="30" t="inlineStr">
-        <is>
-          <t>% (예: 20 = +20%)</t>
-        </is>
-      </c>
-      <c r="D65" s="30" t="inlineStr">
-        <is>
-          <t>시전 바 진행 속도·소환수 공격 주기·불꽃 작렬 충전 속도 증가</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" s="13">
       <c r="A66" s="25" t="inlineStr">
         <is>
-          <t>치명타%(crit)</t>
+          <t>주문력%(spPct)</t>
         </is>
       </c>
       <c r="B66" s="26" t="inlineStr">
         <is>
-          <t>crit</t>
+          <t>spPct</t>
         </is>
       </c>
       <c r="C66" s="27" t="inlineStr">
         <is>
-          <t>%p (예: 10 = +10%, 기본 5%)</t>
+          <t>% (예: 15 = +15%)</t>
         </is>
       </c>
       <c r="D66" s="27" t="inlineStr">
         <is>
-          <t>모든 공격의 치명타 확률 증가 (몰열 2연속 발동에 핵심 기여)</t>
+          <t>기본 주문력 100에 곱해져 모든 피해량이 증가</t>
         </is>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" s="13">
       <c r="A67" s="28" t="inlineStr">
         <is>
-          <t>치명피해%(critDmg)</t>
+          <t>가속%(haste)</t>
         </is>
       </c>
       <c r="B67" s="29" t="inlineStr">
         <is>
-          <t>critDmg</t>
+          <t>haste</t>
         </is>
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>% (예: 35 = +35%)</t>
+          <t>% (예: 20 = +20%)</t>
         </is>
       </c>
       <c r="D67" s="30" t="inlineStr">
         <is>
-          <t>치명타 발생 시 기본 150% 피해 배율에 가산</t>
+          <t>시전 바 진행 속도·소환수 공격 주기·불꽃 작렬 충전 속도 증가</t>
         </is>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" s="13">
       <c r="A68" s="25" t="inlineStr">
         <is>
-          <t>지속피해%(burnPct)</t>
+          <t>치명타%(crit)</t>
         </is>
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>burnPct</t>
+          <t>crit</t>
         </is>
       </c>
       <c r="C68" s="27" t="inlineStr">
         <is>
-          <t>% (예: 45 = +45%)</t>
+          <t>%p (예: 10 = +10%, 기본 5%)</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr">
         <is>
-          <t>화상·메테오 연소·불장판 지속 피해 증가</t>
+          <t>모든 공격의 치명타 확률 증가 (몰열 2연속 발동에 핵심 기여)</t>
         </is>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" s="13">
       <c r="A69" s="28" t="inlineStr">
         <is>
+          <t>치명피해%(critDmg)</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>critDmg</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>% (예: 35 = +35%)</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>치명타 발생 시 기본 150% 피해 배율에 가산</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1" s="13">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>지속피해%(burnPct)</t>
+        </is>
+      </c>
+      <c r="B70" s="26" t="inlineStr">
+        <is>
+          <t>burnPct</t>
+        </is>
+      </c>
+      <c r="C70" s="27" t="inlineStr">
+        <is>
+          <t>% (예: 45 = +45%)</t>
+        </is>
+      </c>
+      <c r="D70" s="27" t="inlineStr">
+        <is>
+          <t>화상·메테오 연소·불장판 지속 피해 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1" s="13">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
           <t>소환수%(spiritPct)</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>spiritPct</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C71" s="30" t="inlineStr">
         <is>
           <t>% (예: 40 = +40%)</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D71" s="30" t="inlineStr">
         <is>
           <t>화염 정령·불사조 피해 증가</t>
         </is>
@@ -3874,18 +3921,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>정령·불사조 등 &lt;b&gt;소환수 피해량이 +60%&lt;/b&gt; 증가합니다.</t>
+          <t>정령·불사조 등 &lt;b&gt;소환수 피해량이 +30%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="I17" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Summon damage +60%&lt;/b&gt; (Fire Spirits, Phoenix).</t>
+          <t>&lt;b&gt;Summon damage +30%&lt;/b&gt; (Fire Spirits, Phoenix).</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       <c r="M17" s="20" t="inlineStr"/>
       <c r="N17" s="20" t="inlineStr"/>
       <c r="O17" s="20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P17" s="19" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>화상·연소·불장판 등 &lt;b&gt;지속 피해량이 +65%&lt;/b&gt; 증가합니다.</t>
+          <t>화상·연소·불장판 등 &lt;b&gt;지속 피해량이 +40%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H21" s="19" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I21" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Damage over time +65%&lt;/b&gt; (Ignite, Meteor burn, Flame Patch).</t>
+          <t>&lt;b&gt;Damage over time +40%&lt;/b&gt; (Ignite, Meteor burn, Flame Patch).</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr"/>
@@ -2249,7 +2249,7 @@
       <c r="L21" s="20" t="inlineStr"/>
       <c r="M21" s="20" t="inlineStr"/>
       <c r="N21" s="20" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="O21" s="20" t="inlineStr"/>
       <c r="P21" s="19" t="inlineStr"/>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="13" customWidth="1" style="13" min="1" max="1"/>
@@ -1010,7 +1010,7 @@
       <c r="S2" s="19" t="inlineStr"/>
       <c r="T2" s="19" t="inlineStr">
         <is>
-          <t>rapid_split, sum_volley, util_glass_cannon</t>
+          <t>rapid_split, sum_volley, util_glass_cannon, crit_ember_verdict</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       <c r="S8" s="19" t="inlineStr"/>
       <c r="T8" s="19" t="inlineStr">
         <is>
-          <t>rapid_split, crit_heat, crit_reckless, spell_meteor, burn_wildfire</t>
+          <t>rapid_split, crit_heat, crit_reckless, spell_meteor, burn_wildfire, crit_ember_verdict</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       <c r="S9" s="19" t="inlineStr"/>
       <c r="T9" s="19" t="inlineStr">
         <is>
-          <t>spell_fireblast, crit_focus, spell_combustion, burn_wildfire</t>
+          <t>spell_fireblast, crit_focus, spell_combustion, burn_wildfire, crit_ember_verdict</t>
         </is>
       </c>
     </row>
@@ -1737,27 +1737,27 @@
     <row r="14" ht="24" customHeight="1" s="13">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>spell_combustion</t>
+          <t>crit_ember_verdict</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>주문서: 마력 폭주</t>
+          <t>불꽃 심판</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>⚖️</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>spell</t>
+          <t>crit</t>
         </is>
       </c>
       <c r="F14" s="20" t="n">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;5초간 모든 마법이 100% 치명타&lt;/b&gt;로 적중하고 시전 속도가 빨라지는 궁극기를 습득합니다.</t>
+          <t>화염구 &lt;b&gt;치명타로 마무리&lt;/b&gt;하면, 다음 스테이지의 첫 화염구 치명타가 &lt;b&gt;8배&lt;/b&gt;로 들어갑니다. (보스는 4배)</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>Grimoire: Combustion</t>
+          <t>Flame Verdict</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>Learn an ultimate: for &lt;b&gt;5s, every spell crits 100%&lt;/b&gt; and you cast faster.</t>
+          <t>Finish a monster with a &lt;b&gt;Fireball crit&lt;/b&gt;, and your first Fireball crit on the next stage deals &lt;b&gt;8×&lt;/b&gt; damage (4× on bosses).</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr"/>
@@ -1785,43 +1785,47 @@
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
       <c r="P14" s="19" t="inlineStr"/>
-      <c r="Q14" s="19" t="inlineStr">
-        <is>
-          <t>combustion</t>
-        </is>
-      </c>
-      <c r="R14" s="19" t="inlineStr"/>
-      <c r="S14" s="19" t="inlineStr"/>
+      <c r="Q14" s="19" t="inlineStr"/>
+      <c r="R14" s="19" t="inlineStr">
+        <is>
+          <t>ember_verdict</t>
+        </is>
+      </c>
+      <c r="S14" s="19" t="inlineStr">
+        <is>
+          <t>{"mult": 8, "bossMult": 4}</t>
+        </is>
+      </c>
       <c r="T14" s="19" t="inlineStr">
         <is>
-          <t>crit_heat, crit_reckless, crit_crimson_frenzy, util_phoenix_reborn, util_auto_grimoire</t>
+          <t>crit_focus, crit_heat, rapid_spark, spell_combustion</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="13">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>crit_crimson_frenzy</t>
+          <t>spell_combustion</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>진홍의 마력 폭주</t>
+          <t>주문서: 마력 폭주</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>👑</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>combustion</t>
+          <t>spell</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
@@ -1829,17 +1833,17 @@
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>마력 폭주 지속 시간이 2배가 되며, 폭주 중 모든 공격 피해가 &lt;b&gt;150% 증폭&lt;/b&gt;됩니다.</t>
+          <t>&lt;b&gt;5초간 모든 마법이 100% 치명타&lt;/b&gt;로 적중하고 시전 속도가 빨라지는 궁극기를 습득합니다.</t>
         </is>
       </c>
       <c r="H15" s="19" t="inlineStr">
         <is>
-          <t>Crimson Combustion</t>
+          <t>Grimoire: Combustion</t>
         </is>
       </c>
       <c r="I15" s="19" t="inlineStr">
         <is>
-          <t>Combustion lasts twice as long, and all damage during it is &lt;b&gt;amplified by 150%&lt;/b&gt;.</t>
+          <t>Learn an ultimate: for &lt;b&gt;5s, every spell crits 100%&lt;/b&gt; and you cast faster.</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr"/>
@@ -1848,66 +1852,62 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="19" t="inlineStr">
-        <is>
-          <t>has_combustion</t>
-        </is>
-      </c>
-      <c r="Q15" s="19" t="inlineStr"/>
-      <c r="R15" s="19" t="inlineStr">
-        <is>
-          <t>combustion_god</t>
-        </is>
-      </c>
+      <c r="P15" s="19" t="inlineStr"/>
+      <c r="Q15" s="19" t="inlineStr">
+        <is>
+          <t>combustion</t>
+        </is>
+      </c>
+      <c r="R15" s="19" t="inlineStr"/>
       <c r="S15" s="19" t="inlineStr"/>
       <c r="T15" s="19" t="inlineStr">
         <is>
-          <t>spell_combustion</t>
+          <t>crit_heat, crit_reckless, crit_crimson_frenzy, util_phoenix_reborn, util_auto_grimoire, crit_ember_verdict</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="13">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>sum_spirit</t>
+          <t>crit_crimson_frenzy</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>화염 정령 소환</t>
+          <t>진홍의 마력 폭주</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>🧞</t>
+          <t>👑</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>combustion</t>
         </is>
       </c>
       <c r="F16" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>플레이어 옆에 지속 화염 공격을 퍼붓는 &lt;b&gt;화염 정령 1기&lt;/b&gt;를 소환합니다 (최대 4기).</t>
+          <t>마력 폭주 지속 시간이 2배가 되며, 폭주 중 모든 공격 피해가 &lt;b&gt;150% 증폭&lt;/b&gt;됩니다.</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>Summon Fire Spirit</t>
+          <t>Crimson Combustion</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
         <is>
-          <t>Summon &lt;b&gt;1 Fire Spirit&lt;/b&gt; that pours fire beside you (up to 4).</t>
+          <t>Combustion lasts twice as long, and all damage during it is &lt;b&gt;amplified by 150%&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr"/>
@@ -1916,34 +1916,38 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="19" t="inlineStr"/>
+      <c r="P16" s="19" t="inlineStr">
+        <is>
+          <t>has_combustion</t>
+        </is>
+      </c>
       <c r="Q16" s="19" t="inlineStr"/>
       <c r="R16" s="19" t="inlineStr">
         <is>
-          <t>extra_spirit</t>
+          <t>combustion_god</t>
         </is>
       </c>
       <c r="S16" s="19" t="inlineStr"/>
       <c r="T16" s="19" t="inlineStr">
         <is>
-          <t>sum_fury, sum_volley, sum_pact, sum_cinder_lord</t>
+          <t>spell_combustion</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="13">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>sum_fury</t>
+          <t>sum_spirit</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>정령의 분노</t>
+          <t>화염 정령 소환</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>😤</t>
+          <t>🧞</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -1957,21 +1961,21 @@
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>정령·불사조 등 &lt;b&gt;소환수 피해량이 +30%&lt;/b&gt; 증가합니다.</t>
+          <t>플레이어 옆에 지속 화염 공격을 퍼붓는 &lt;b&gt;화염 정령 1기&lt;/b&gt;를 소환합니다 (최대 4기).</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr">
         <is>
-          <t>Spirit Fury</t>
+          <t>Summon Fire Spirit</t>
         </is>
       </c>
       <c r="I17" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Summon damage +30%&lt;/b&gt; (Fire Spirits, Phoenix).</t>
+          <t>Summon &lt;b&gt;1 Fire Spirit&lt;/b&gt; that pours fire beside you (up to 4).</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr"/>
@@ -1979,42 +1983,40 @@
       <c r="L17" s="20" t="inlineStr"/>
       <c r="M17" s="20" t="inlineStr"/>
       <c r="N17" s="20" t="inlineStr"/>
-      <c r="O17" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="P17" s="19" t="inlineStr">
-        <is>
-          <t>has_summon</t>
-        </is>
-      </c>
+      <c r="O17" s="20" t="inlineStr"/>
+      <c r="P17" s="19" t="inlineStr"/>
       <c r="Q17" s="19" t="inlineStr"/>
-      <c r="R17" s="19" t="inlineStr"/>
+      <c r="R17" s="19" t="inlineStr">
+        <is>
+          <t>extra_spirit</t>
+        </is>
+      </c>
       <c r="S17" s="19" t="inlineStr"/>
       <c r="T17" s="19" t="inlineStr">
         <is>
-          <t>sum_spirit</t>
+          <t>sum_fury, sum_volley, sum_pact, sum_cinder_lord</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="13">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>sum_volley</t>
+          <t>sum_fury</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>일제 협공 사격</t>
+          <t>정령의 분노</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>🏹</t>
+          <t>😤</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -2023,21 +2025,21 @@
         </is>
       </c>
       <c r="F18" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>마법사가 화염구를 발사할 때마다 &lt;b&gt;소환된 모든 정령이 동시에 협공 탄환&lt;/b&gt;을 발사합니다.</t>
+          <t>정령·불사조 등 &lt;b&gt;소환수 피해량이 +30%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>Synchronized Volley</t>
+          <t>Spirit Fury</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>Every time you cast Fireball, &lt;b&gt;all summoned spirits fire a volley at once&lt;/b&gt;.</t>
+          <t>&lt;b&gt;Summon damage +30%&lt;/b&gt; (Fire Spirits, Phoenix).</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr"/>
@@ -2045,39 +2047,37 @@
       <c r="L18" s="20" t="inlineStr"/>
       <c r="M18" s="20" t="inlineStr"/>
       <c r="N18" s="20" t="inlineStr"/>
-      <c r="O18" s="20" t="inlineStr"/>
+      <c r="O18" s="20" t="n">
+        <v>30</v>
+      </c>
       <c r="P18" s="19" t="inlineStr">
         <is>
           <t>has_summon</t>
         </is>
       </c>
       <c r="Q18" s="19" t="inlineStr"/>
-      <c r="R18" s="19" t="inlineStr">
-        <is>
-          <t>synchronized_fire</t>
-        </is>
-      </c>
+      <c r="R18" s="19" t="inlineStr"/>
       <c r="S18" s="19" t="inlineStr"/>
       <c r="T18" s="19" t="inlineStr">
         <is>
-          <t>rapid_spark, rapid_gatling, sum_spirit</t>
+          <t>sum_spirit</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="13">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>sum_pact</t>
+          <t>sum_volley</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>정령 계약</t>
+          <t>일제 협공 사격</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>🤝</t>
+          <t>🏹</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -2095,62 +2095,62 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>소환수 피해량이 &lt;b&gt;+100%&lt;/b&gt; 증가하지만, 마법사의 주문력이 &lt;b&gt;-25%&lt;/b&gt; 감소합니다.</t>
+          <t>마법사가 화염구를 발사할 때마다 &lt;b&gt;소환된 모든 정령이 동시에 협공 탄환&lt;/b&gt;을 발사합니다.</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
-          <t>Spirit Pact</t>
+          <t>Synchronized Volley</t>
         </is>
       </c>
       <c r="I19" s="19" t="inlineStr">
         <is>
-          <t>Summon damage &lt;b&gt;+100%&lt;/b&gt;, but your Spell Power &lt;b&gt;-25%&lt;/b&gt;.</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="n">
-        <v>-25</v>
-      </c>
+          <t>Every time you cast Fireball, &lt;b&gt;all summoned spirits fire a volley at once&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr"/>
       <c r="K19" s="20" t="inlineStr"/>
       <c r="L19" s="20" t="inlineStr"/>
       <c r="M19" s="20" t="inlineStr"/>
       <c r="N19" s="20" t="inlineStr"/>
-      <c r="O19" s="20" t="n">
-        <v>100</v>
-      </c>
+      <c r="O19" s="20" t="inlineStr"/>
       <c r="P19" s="19" t="inlineStr">
         <is>
           <t>has_summon</t>
         </is>
       </c>
       <c r="Q19" s="19" t="inlineStr"/>
-      <c r="R19" s="19" t="inlineStr"/>
+      <c r="R19" s="19" t="inlineStr">
+        <is>
+          <t>synchronized_fire</t>
+        </is>
+      </c>
       <c r="S19" s="19" t="inlineStr"/>
       <c r="T19" s="19" t="inlineStr">
         <is>
-          <t>sum_spirit, sum_cinder_lord</t>
+          <t>rapid_spark, rapid_gatling, sum_spirit</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="13">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>sum_cinder_lord</t>
+          <t>sum_pact</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>잿더미 군단장</t>
+          <t>정령 계약</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>👹</t>
+          <t>🤝</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -2163,183 +2163,187 @@
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>소환수 1기당 마법사의 모든 주문 피해량이 &lt;b&gt;+30%&lt;/b&gt; 증폭됩니다.</t>
+          <t>소환수 피해량이 &lt;b&gt;+100%&lt;/b&gt; 증가하지만, 마법사의 주문력이 &lt;b&gt;-25%&lt;/b&gt; 감소합니다.</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>Cinder Warlord</t>
+          <t>Spirit Pact</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>All your spell damage &lt;b&gt;+30%&lt;/b&gt; per active summon.</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr"/>
+          <t>Summon damage &lt;b&gt;+100%&lt;/b&gt;, but your Spell Power &lt;b&gt;-25%&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="n">
+        <v>-25</v>
+      </c>
       <c r="K20" s="20" t="inlineStr"/>
       <c r="L20" s="20" t="inlineStr"/>
       <c r="M20" s="20" t="inlineStr"/>
       <c r="N20" s="20" t="inlineStr"/>
-      <c r="O20" s="20" t="inlineStr"/>
+      <c r="O20" s="20" t="n">
+        <v>100</v>
+      </c>
       <c r="P20" s="19" t="inlineStr">
         <is>
           <t>has_summon</t>
         </is>
       </c>
       <c r="Q20" s="19" t="inlineStr"/>
-      <c r="R20" s="19" t="inlineStr">
-        <is>
-          <t>cinder_lord</t>
-        </is>
-      </c>
+      <c r="R20" s="19" t="inlineStr"/>
       <c r="S20" s="19" t="inlineStr"/>
       <c r="T20" s="19" t="inlineStr">
         <is>
-          <t>sum_spirit, sum_pact</t>
+          <t>sum_spirit, sum_cinder_lord</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="13">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>burn_ignite</t>
+          <t>sum_cinder_lord</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>맹렬한 화상</t>
+          <t>잿더미 군단장</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>🩸</t>
+          <t>👹</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>burn</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>화상·연소·불장판 등 &lt;b&gt;지속 피해량이 +40%&lt;/b&gt; 증가합니다.</t>
+          <t>소환수 1기당 마법사의 모든 주문 피해량이 &lt;b&gt;+30%&lt;/b&gt; 증폭됩니다.</t>
         </is>
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>Fierce Ignite</t>
+          <t>Cinder Warlord</t>
         </is>
       </c>
       <c r="I21" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Damage over time +40%&lt;/b&gt; (Ignite, Meteor burn, Flame Patch).</t>
+          <t>All your spell damage &lt;b&gt;+30%&lt;/b&gt; per active summon.</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr"/>
       <c r="K21" s="20" t="inlineStr"/>
       <c r="L21" s="20" t="inlineStr"/>
       <c r="M21" s="20" t="inlineStr"/>
-      <c r="N21" s="20" t="n">
-        <v>40</v>
-      </c>
+      <c r="N21" s="20" t="inlineStr"/>
       <c r="O21" s="20" t="inlineStr"/>
-      <c r="P21" s="19" t="inlineStr"/>
+      <c r="P21" s="19" t="inlineStr">
+        <is>
+          <t>has_summon</t>
+        </is>
+      </c>
       <c r="Q21" s="19" t="inlineStr"/>
-      <c r="R21" s="19" t="inlineStr"/>
+      <c r="R21" s="19" t="inlineStr">
+        <is>
+          <t>cinder_lord</t>
+        </is>
+      </c>
       <c r="S21" s="19" t="inlineStr"/>
       <c r="T21" s="19" t="inlineStr">
         <is>
-          <t>spell_meteor, spell_flame_patch, burn_wildfire</t>
+          <t>sum_spirit, sum_pact</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="13">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>spell_flame_patch</t>
+          <t>burn_ignite</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>주문서: 불장판</t>
+          <t>맹렬한 화상</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>🌋</t>
+          <t>🩸</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>spell</t>
+          <t>burn</t>
         </is>
       </c>
       <c r="F22" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="19" t="inlineStr">
         <is>
-          <t>몬스터 발밑에 지속적인 화염 지대를 생성하여 &lt;b&gt;강력한 화상 도트 피해&lt;/b&gt;를 입힙니다.</t>
+          <t>화상·연소·불장판 등 &lt;b&gt;지속 피해량이 +40%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>Grimoire: Flame Patch</t>
+          <t>Fierce Ignite</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>Create a lasting fire zone under the monster that deals &lt;b&gt;heavy burning damage over time&lt;/b&gt;.</t>
+          <t>&lt;b&gt;Damage over time +40%&lt;/b&gt; (Ignite, Meteor burn, Flame Patch).</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr"/>
       <c r="K22" s="20" t="inlineStr"/>
       <c r="L22" s="20" t="inlineStr"/>
       <c r="M22" s="20" t="inlineStr"/>
-      <c r="N22" s="20" t="inlineStr"/>
+      <c r="N22" s="20" t="n">
+        <v>40</v>
+      </c>
       <c r="O22" s="20" t="inlineStr"/>
       <c r="P22" s="19" t="inlineStr"/>
-      <c r="Q22" s="19" t="inlineStr">
-        <is>
-          <t>flame_patch</t>
-        </is>
-      </c>
+      <c r="Q22" s="19" t="inlineStr"/>
       <c r="R22" s="19" t="inlineStr"/>
       <c r="S22" s="19" t="inlineStr"/>
       <c r="T22" s="19" t="inlineStr">
         <is>
-          <t>burn_ignite, burn_spread, util_phoenix_reborn, util_auto_grimoire</t>
+          <t>spell_meteor, spell_flame_patch, burn_wildfire</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" s="13">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>burn_spread</t>
+          <t>spell_flame_patch</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>번지는 불길</t>
+          <t>주문서: 불장판</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>♨️</t>
+          <t>🌋</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -2349,25 +2353,25 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>burn</t>
+          <t>spell</t>
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="19" t="inlineStr">
         <is>
-          <t>불장판 재사용 대기시간이 &lt;b&gt;30% 감소&lt;/b&gt;하고 불장판 피해량이 &lt;b&gt;+50%&lt;/b&gt; 증가합니다.</t>
+          <t>몬스터 발밑에 지속적인 화염 지대를 생성하여 &lt;b&gt;강력한 화상 도트 피해&lt;/b&gt;를 입힙니다.</t>
         </is>
       </c>
       <c r="H23" s="19" t="inlineStr">
         <is>
-          <t>Spreading Blaze</t>
+          <t>Grimoire: Flame Patch</t>
         </is>
       </c>
       <c r="I23" s="19" t="inlineStr">
         <is>
-          <t>Flame Patch cooldown &lt;b&gt;-30%&lt;/b&gt; and Flame Patch damage &lt;b&gt;+50%&lt;/b&gt;.</t>
+          <t>Create a lasting fire zone under the monster that deals &lt;b&gt;heavy burning damage over time&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr"/>
@@ -2376,47 +2380,39 @@
       <c r="M23" s="20" t="inlineStr"/>
       <c r="N23" s="20" t="inlineStr"/>
       <c r="O23" s="20" t="inlineStr"/>
-      <c r="P23" s="19" t="inlineStr">
-        <is>
-          <t>has_flame_patch</t>
-        </is>
-      </c>
-      <c r="Q23" s="19" t="inlineStr"/>
-      <c r="R23" s="19" t="inlineStr">
-        <is>
-          <t>patch_boost</t>
-        </is>
-      </c>
-      <c r="S23" s="19" t="inlineStr">
-        <is>
-          <t>{"cooldownMult": 0.7, "damageBonus": 0.5}</t>
-        </is>
-      </c>
+      <c r="P23" s="19" t="inlineStr"/>
+      <c r="Q23" s="19" t="inlineStr">
+        <is>
+          <t>flame_patch</t>
+        </is>
+      </c>
+      <c r="R23" s="19" t="inlineStr"/>
+      <c r="S23" s="19" t="inlineStr"/>
       <c r="T23" s="19" t="inlineStr">
         <is>
-          <t>spell_flame_patch</t>
+          <t>burn_ignite, burn_spread, util_phoenix_reborn, util_auto_grimoire</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" s="13">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>burn_wildfire</t>
+          <t>burn_spread</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>들불</t>
+          <t>번지는 불길</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>🌋</t>
+          <t>♨️</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -2425,21 +2421,21 @@
         </is>
       </c>
       <c r="F24" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;모든 적중이 화상&lt;/b&gt;을 남기고, 치명타가 남기는 &lt;b&gt;화상 피해는 6배&lt;/b&gt;로 불어납니다. 쓰러진 적의 &lt;b&gt;남은 화상은 다음 적에게 번집니다&lt;/b&gt;.</t>
+          <t>불장판 재사용 대기시간이 &lt;b&gt;30% 감소&lt;/b&gt;하고 불장판 피해량이 &lt;b&gt;+50%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Spreading Blaze</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Every hit leaves Ignite&lt;/b&gt;, and Ignite from critical strikes deals &lt;b&gt;6x damage&lt;/b&gt;. Leftover Ignite &lt;b&gt;spreads to the next enemy&lt;/b&gt;.</t>
+          <t>Flame Patch cooldown &lt;b&gt;-30%&lt;/b&gt; and Flame Patch damage &lt;b&gt;+50%&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr"/>
@@ -2448,71 +2444,73 @@
       <c r="M24" s="20" t="inlineStr"/>
       <c r="N24" s="20" t="inlineStr"/>
       <c r="O24" s="20" t="inlineStr"/>
-      <c r="P24" s="19" t="inlineStr"/>
+      <c r="P24" s="19" t="inlineStr">
+        <is>
+          <t>has_flame_patch</t>
+        </is>
+      </c>
       <c r="Q24" s="19" t="inlineStr"/>
       <c r="R24" s="19" t="inlineStr">
         <is>
-          <t>wildfire</t>
+          <t>patch_boost</t>
         </is>
       </c>
       <c r="S24" s="19" t="inlineStr">
         <is>
-          <t>{"igniteRatioMult": 6, "igniteOnAllHits": true, "igniteCarryOver": true}</t>
+          <t>{"cooldownMult": 0.7, "damageBonus": 0.5}</t>
         </is>
       </c>
       <c r="T24" s="19" t="inlineStr">
         <is>
-          <t>crit_focus, crit_heat, burn_ignite</t>
+          <t>spell_flame_patch</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" s="13">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>util_power</t>
+          <t>burn_wildfire</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>마력 증폭</t>
+          <t>들불</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>🔮</t>
+          <t>🌋</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>legendary</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>utility</t>
+          <t>burn</t>
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>주문력이 &lt;b&gt;+22%&lt;/b&gt; 증가합니다.</t>
+          <t>&lt;b&gt;모든 적중이 화상&lt;/b&gt;을 남기고, 치명타가 남기는 &lt;b&gt;화상 피해는 6배&lt;/b&gt;로 불어납니다. 쓰러진 적의 &lt;b&gt;남은 화상은 다음 적에게 번집니다&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
         <is>
-          <t>Arcane Amplify</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="I25" s="19" t="inlineStr">
         <is>
-          <t>Spell Power &lt;b&gt;+22%&lt;/b&gt;.</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="n">
-        <v>22</v>
-      </c>
+          <t>&lt;b&gt;Every hit leaves Ignite&lt;/b&gt;, and Ignite from critical strikes deals &lt;b&gt;6x damage&lt;/b&gt;. Leftover Ignite &lt;b&gt;spreads to the next enemy&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr"/>
       <c r="K25" s="20" t="inlineStr"/>
       <c r="L25" s="20" t="inlineStr"/>
       <c r="M25" s="20" t="inlineStr"/>
@@ -2520,33 +2518,41 @@
       <c r="O25" s="20" t="inlineStr"/>
       <c r="P25" s="19" t="inlineStr"/>
       <c r="Q25" s="19" t="inlineStr"/>
-      <c r="R25" s="19" t="inlineStr"/>
-      <c r="S25" s="19" t="inlineStr"/>
+      <c r="R25" s="19" t="inlineStr">
+        <is>
+          <t>wildfire</t>
+        </is>
+      </c>
+      <c r="S25" s="19" t="inlineStr">
+        <is>
+          <t>{"igniteRatioMult": 6, "igniteOnAllHits": true, "igniteCarryOver": true}</t>
+        </is>
+      </c>
       <c r="T25" s="19" t="inlineStr">
         <is>
-          <t>util_executioner</t>
+          <t>crit_focus, crit_heat, burn_ignite</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" s="13">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>util_executioner</t>
+          <t>util_power</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>처형인의 불꽃</t>
+          <t>마력 증폭</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>☠️</t>
+          <t>🔮</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -2555,24 +2561,26 @@
         </is>
       </c>
       <c r="F26" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>체력이 40% 이하인 적에게 입히는 모든 피해량이 &lt;b&gt;+70%&lt;/b&gt; 증가합니다.</t>
+          <t>주문력이 &lt;b&gt;+22%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>Executioner's Flame</t>
+          <t>Arcane Amplify</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
         <is>
-          <t>All damage to enemies at or below 40% health &lt;b&gt;+70%&lt;/b&gt;.</t>
-        </is>
-      </c>
-      <c r="J26" s="20" t="inlineStr"/>
+          <t>Spell Power &lt;b&gt;+22%&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="n">
+        <v>22</v>
+      </c>
       <c r="K26" s="20" t="inlineStr"/>
       <c r="L26" s="20" t="inlineStr"/>
       <c r="M26" s="20" t="inlineStr"/>
@@ -2580,36 +2588,28 @@
       <c r="O26" s="20" t="inlineStr"/>
       <c r="P26" s="19" t="inlineStr"/>
       <c r="Q26" s="19" t="inlineStr"/>
-      <c r="R26" s="19" t="inlineStr">
-        <is>
-          <t>executioner</t>
-        </is>
-      </c>
-      <c r="S26" s="19" t="inlineStr">
-        <is>
-          <t>{"executionerMult": 0.7}</t>
-        </is>
-      </c>
+      <c r="R26" s="19" t="inlineStr"/>
+      <c r="S26" s="19" t="inlineStr"/>
       <c r="T26" s="19" t="inlineStr">
         <is>
-          <t>util_power</t>
+          <t>util_executioner</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="13">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>util_glass_cannon</t>
+          <t>util_executioner</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>유리 대포</t>
+          <t>처형인의 불꽃</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>💎</t>
+          <t>☠️</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -2627,58 +2627,62 @@
       </c>
       <c r="G27" s="19" t="inlineStr">
         <is>
-          <t>주문력이 &lt;b&gt;+50%&lt;/b&gt; 증가하지만, 시전 속도가 &lt;b&gt;-25%&lt;/b&gt; 느려집니다.</t>
+          <t>체력이 40% 이하인 적에게 입히는 모든 피해량이 &lt;b&gt;+70%&lt;/b&gt; 증가합니다.</t>
         </is>
       </c>
       <c r="H27" s="19" t="inlineStr">
         <is>
-          <t>Glass Cannon</t>
+          <t>Executioner's Flame</t>
         </is>
       </c>
       <c r="I27" s="19" t="inlineStr">
         <is>
-          <t>Spell Power &lt;b&gt;+50%&lt;/b&gt;, but cast speed &lt;b&gt;-25%&lt;/b&gt;.</t>
-        </is>
-      </c>
-      <c r="J27" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="K27" s="20" t="n">
-        <v>-25</v>
-      </c>
+          <t>All damage to enemies at or below 40% health &lt;b&gt;+70%&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr"/>
+      <c r="K27" s="20" t="inlineStr"/>
       <c r="L27" s="20" t="inlineStr"/>
       <c r="M27" s="20" t="inlineStr"/>
       <c r="N27" s="20" t="inlineStr"/>
       <c r="O27" s="20" t="inlineStr"/>
       <c r="P27" s="19" t="inlineStr"/>
       <c r="Q27" s="19" t="inlineStr"/>
-      <c r="R27" s="19" t="inlineStr"/>
-      <c r="S27" s="19" t="inlineStr"/>
+      <c r="R27" s="19" t="inlineStr">
+        <is>
+          <t>executioner</t>
+        </is>
+      </c>
+      <c r="S27" s="19" t="inlineStr">
+        <is>
+          <t>{"executionerMult": 0.7}</t>
+        </is>
+      </c>
       <c r="T27" s="19" t="inlineStr">
         <is>
-          <t>rapid_spark, rapid_overload</t>
+          <t>util_power</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="13">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>util_phoenix_reborn</t>
+          <t>util_glass_cannon</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>불사조의 가호</t>
+          <t>유리 대포</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>🪶</t>
+          <t>💎</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>legendary</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -2687,61 +2691,57 @@
         </is>
       </c>
       <c r="F28" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;불사조&lt;/b&gt;가 함께 싸우며 확정 치명타로 협공하고, 치명타 적중 시 &lt;b&gt;10% 확률로 모든 스킬 쿨다운&lt;/b&gt;이 초기화됩니다.</t>
+          <t>주문력이 &lt;b&gt;+50%&lt;/b&gt; 증가하지만, 시전 속도가 &lt;b&gt;-25%&lt;/b&gt; 느려집니다.</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
         <is>
-          <t>Phoenix's Blessing</t>
+          <t>Glass Cannon</t>
         </is>
       </c>
       <c r="I28" s="19" t="inlineStr">
         <is>
-          <t>A &lt;b&gt;Phoenix&lt;/b&gt; fights at your side with guaranteed crits, and your crits have a &lt;b&gt;10% chance to reset all skill cooldowns&lt;/b&gt;.</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr"/>
-      <c r="K28" s="20" t="inlineStr"/>
+          <t>Spell Power &lt;b&gt;+50%&lt;/b&gt;, but cast speed &lt;b&gt;-25%&lt;/b&gt;.</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="K28" s="20" t="n">
+        <v>-25</v>
+      </c>
       <c r="L28" s="20" t="inlineStr"/>
       <c r="M28" s="20" t="inlineStr"/>
       <c r="N28" s="20" t="inlineStr"/>
       <c r="O28" s="20" t="inlineStr"/>
-      <c r="P28" s="19" t="inlineStr">
-        <is>
-          <t>has_any_spell</t>
-        </is>
-      </c>
+      <c r="P28" s="19" t="inlineStr"/>
       <c r="Q28" s="19" t="inlineStr"/>
-      <c r="R28" s="19" t="inlineStr">
-        <is>
-          <t>phoenix_reset</t>
-        </is>
-      </c>
+      <c r="R28" s="19" t="inlineStr"/>
       <c r="S28" s="19" t="inlineStr"/>
       <c r="T28" s="19" t="inlineStr">
         <is>
-          <t>spell_meteor, spell_combustion, spell_flame_patch</t>
+          <t>rapid_spark, rapid_overload</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="13">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>util_auto_grimoire</t>
+          <t>util_phoenix_reborn</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>자동 영창</t>
+          <t>불사조의 가호</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>🤖</t>
+          <t>🪶</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>화염구 외 모든 주문(불꽃 작렬·메테오·마력 폭주·불장판)이 &lt;b&gt;최적의 순간에 자동 시전&lt;/b&gt;됩니다. 주문 칸의 &lt;b&gt;AUTO&lt;/b&gt;를 눌러 주문별로 끄고 켤 수 있습니다.</t>
+          <t>&lt;b&gt;불사조&lt;/b&gt;가 함께 싸우며 확정 치명타로 협공하고, 치명타 적중 시 &lt;b&gt;10% 확률로 모든 스킬 쿨다운&lt;/b&gt;이 초기화됩니다.</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr">
         <is>
-          <t>Auto-Incantation</t>
+          <t>Phoenix's Blessing</t>
         </is>
       </c>
       <c r="I29" s="19" t="inlineStr">
         <is>
-          <t>Every spell besides Fireball (Fire Blast, Meteor, Combustion, Flame Patch) &lt;b&gt;casts itself at the perfect moment&lt;/b&gt;. Tap a slot's &lt;b&gt;AUTO&lt;/b&gt; tag to toggle each spell.</t>
+          <t>A &lt;b&gt;Phoenix&lt;/b&gt; fights at your side with guaranteed crits, and your crits have a &lt;b&gt;10% chance to reset all skill cooldowns&lt;/b&gt;.</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr"/>
@@ -2786,11 +2786,79 @@
       <c r="Q29" s="19" t="inlineStr"/>
       <c r="R29" s="19" t="inlineStr">
         <is>
-          <t>smart_autocast</t>
+          <t>phoenix_reset</t>
         </is>
       </c>
       <c r="S29" s="19" t="inlineStr"/>
       <c r="T29" s="19" t="inlineStr">
+        <is>
+          <t>spell_meteor, spell_combustion, spell_flame_patch</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" s="13">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>util_auto_grimoire</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>자동 영창</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>legendary</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>utility</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>화염구 외 모든 주문(불꽃 작렬·메테오·마력 폭주·불장판)이 &lt;b&gt;최적의 순간에 자동 시전&lt;/b&gt;됩니다. 주문 칸의 &lt;b&gt;AUTO&lt;/b&gt;를 눌러 주문별로 끄고 켤 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="inlineStr">
+        <is>
+          <t>Auto-Incantation</t>
+        </is>
+      </c>
+      <c r="I30" s="19" t="inlineStr">
+        <is>
+          <t>Every spell besides Fireball (Fire Blast, Meteor, Combustion, Flame Patch) &lt;b&gt;casts itself at the perfect moment&lt;/b&gt;. Tap a slot's &lt;b&gt;AUTO&lt;/b&gt; tag to toggle each spell.</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr"/>
+      <c r="K30" s="20" t="inlineStr"/>
+      <c r="L30" s="20" t="inlineStr"/>
+      <c r="M30" s="20" t="inlineStr"/>
+      <c r="N30" s="20" t="inlineStr"/>
+      <c r="O30" s="20" t="inlineStr"/>
+      <c r="P30" s="19" t="inlineStr">
+        <is>
+          <t>has_any_spell</t>
+        </is>
+      </c>
+      <c r="Q30" s="19" t="inlineStr"/>
+      <c r="R30" s="19" t="inlineStr">
+        <is>
+          <t>smart_autocast</t>
+        </is>
+      </c>
+      <c r="S30" s="19" t="inlineStr"/>
+      <c r="T30" s="19" t="inlineStr">
         <is>
           <t>spell_fireblast, spell_meteor, spell_combustion, spell_flame_patch</t>
         </is>
@@ -2810,8 +2878,8 @@
     <dataValidation sqref="Q2:Q100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(fireblast, meteor, combustion, flame_patch)에서 선택하거나 빈칸으로 두세요." promptTitle="[해금스킬(spellKey) 안내]" prompt="• fireblast: 불꽃 작렬&#10;• meteor: 메테오&#10;• combustion: 마력 폭주&#10;• flame_patch: 불장판" type="list">
       <formula1>"fireblast,meteor,combustion,flame_patch"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(split_fireball, gatling_mode, quickdraw_charge, meteor_buff, meteor_charge, combustion_god, extra_spirit, synchronized_fire, cinder_lord, patch_boost, wildfire, executioner, phoenix_reset, smart_autocast)에서 선택하거나 빈칸으로 두세요." promptTitle="[특수기믹(mechanic) 안내]" prompt="시스템 특수 로직 키입니다.&#10;효과와 파라미터는 [📖 옵션_도움말_가이드] 탭을 확인하세요!" type="list">
-      <formula1>"split_fireball,gatling_mode,quickdraw_charge,meteor_buff,meteor_charge,combustion_god,extra_spirit,synchronized_fire,cinder_lord,patch_boost,wildfire,executioner,phoenix_reset,smart_autocast"</formula1>
+    <dataValidation sqref="R2:R100" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="유효하지 않은 값" error="목록(split_fireball, gatling_mode, quickdraw_charge, meteor_buff, meteor_charge, combustion_god, extra_spirit, synchronized_fire, cinder_lord, patch_boost, wildfire, executioner, phoenix_reset, smart_autocast, ember_verdict)에서 선택하거나 빈칸으로 두세요." promptTitle="[특수기믹(mechanic) 안내]" prompt="시스템 특수 로직 키입니다.&#10;효과와 파라미터는 [📖 옵션_도움말_가이드] 탭을 확인하세요!" type="list">
+      <formula1>"split_fireball,gatling_mode,quickdraw_charge,meteor_buff,meteor_charge,combustion_god,extra_spirit,synchronized_fire,cinder_lord,patch_boost,wildfire,executioner,phoenix_reset,smart_autocast,ember_verdict"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2825,7 +2893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="13" min="1" max="1"/>
@@ -3732,188 +3800,210 @@
     <row r="60" ht="22" customHeight="1" s="13">
       <c r="A60" s="28" t="inlineStr">
         <is>
+          <t>ember_verdict</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>불꽃 심판</t>
+        </is>
+      </c>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>화염구 치명타로 몬스터를 처치하면, 다음 스테이지의 첫 화염구 치명타가 mult배(보스는 bossMult배)로 들어갑니다.</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>{"mult": 8, "bossMult": 4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1" s="13">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
           <t>smart_autocast</t>
         </is>
       </c>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="B61" s="26" t="inlineStr">
         <is>
           <t>자동 영창</t>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
+      <c r="C61" s="27" t="inlineStr">
         <is>
           <t>화염구 외 주문(불꽃 작렬·메테오·마력 폭주·불장판)도 최적의 순간에 자동 시전합니다. 없으면 이 주문들은 직접 눌러야 합니다.</t>
         </is>
       </c>
-      <c r="D60" s="30" t="inlineStr">
+      <c r="D61" s="27" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="26" customHeight="1" s="13">
-      <c r="A63" s="22" t="inlineStr">
+    <row r="64" ht="26" customHeight="1" s="13">
+      <c r="A64" s="22" t="inlineStr">
         <is>
           <t>6. 스탯 (stats) 컬럼 가이드</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1" s="13">
-      <c r="A64" s="23" t="inlineStr">
+    <row r="65" ht="20" customHeight="1" s="13">
+      <c r="A65" s="23" t="inlineStr">
         <is>
           <t>카드 습득 시 런(Run) 동안 누적되는 스탯입니다. 모든 값은 정수 퍼센트로 입력하며, 대가형 카드는 음수로 손해를 표현합니다.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="24" customHeight="1" s="13">
-      <c r="A65" s="24" t="inlineStr">
+    <row r="66" ht="24" customHeight="1" s="13">
+      <c r="A66" s="24" t="inlineStr">
         <is>
           <t>열 이름</t>
         </is>
       </c>
-      <c r="B65" s="24" t="inlineStr">
+      <c r="B66" s="24" t="inlineStr">
         <is>
           <t>스탯 키</t>
         </is>
       </c>
-      <c r="C65" s="24" t="inlineStr">
+      <c r="C66" s="24" t="inlineStr">
         <is>
           <t>단위 및 계산 방식</t>
         </is>
       </c>
-      <c r="D65" s="24" t="inlineStr">
+      <c r="D66" s="24" t="inlineStr">
         <is>
           <t>인게임 효과</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="22" customHeight="1" s="13">
-      <c r="A66" s="25" t="inlineStr">
+    <row r="67" ht="22" customHeight="1" s="13">
+      <c r="A67" s="25" t="inlineStr">
         <is>
           <t>주문력%(spPct)</t>
         </is>
       </c>
-      <c r="B66" s="26" t="inlineStr">
+      <c r="B67" s="26" t="inlineStr">
         <is>
           <t>spPct</t>
         </is>
       </c>
-      <c r="C66" s="27" t="inlineStr">
+      <c r="C67" s="27" t="inlineStr">
         <is>
           <t>% (예: 15 = +15%)</t>
         </is>
       </c>
-      <c r="D66" s="27" t="inlineStr">
+      <c r="D67" s="27" t="inlineStr">
         <is>
           <t>기본 주문력 100에 곱해져 모든 피해량이 증가</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1" s="13">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="68" ht="22" customHeight="1" s="13">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>가속%(haste)</t>
         </is>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>haste</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>% (예: 20 = +20%)</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>시전 바 진행 속도·소환수 공격 주기·불꽃 작렬 충전 속도 증가</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="22" customHeight="1" s="13">
-      <c r="A68" s="25" t="inlineStr">
+    <row r="69" ht="22" customHeight="1" s="13">
+      <c r="A69" s="25" t="inlineStr">
         <is>
           <t>치명타%(crit)</t>
         </is>
       </c>
-      <c r="B68" s="26" t="inlineStr">
+      <c r="B69" s="26" t="inlineStr">
         <is>
           <t>crit</t>
         </is>
       </c>
-      <c r="C68" s="27" t="inlineStr">
+      <c r="C69" s="27" t="inlineStr">
         <is>
           <t>%p (예: 10 = +10%, 기본 5%)</t>
         </is>
       </c>
-      <c r="D68" s="27" t="inlineStr">
+      <c r="D69" s="27" t="inlineStr">
         <is>
           <t>모든 공격의 치명타 확률 증가 (몰열 2연속 발동에 핵심 기여)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="22" customHeight="1" s="13">
-      <c r="A69" s="28" t="inlineStr">
+    <row r="70" ht="22" customHeight="1" s="13">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>치명피해%(critDmg)</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>critDmg</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>% (예: 35 = +35%)</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>치명타 발생 시 기본 150% 피해 배율에 가산</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="22" customHeight="1" s="13">
-      <c r="A70" s="25" t="inlineStr">
+    <row r="71" ht="22" customHeight="1" s="13">
+      <c r="A71" s="25" t="inlineStr">
         <is>
           <t>지속피해%(burnPct)</t>
         </is>
       </c>
-      <c r="B70" s="26" t="inlineStr">
+      <c r="B71" s="26" t="inlineStr">
         <is>
           <t>burnPct</t>
         </is>
       </c>
-      <c r="C70" s="27" t="inlineStr">
+      <c r="C71" s="27" t="inlineStr">
         <is>
           <t>% (예: 45 = +45%)</t>
         </is>
       </c>
-      <c r="D70" s="27" t="inlineStr">
+      <c r="D71" s="27" t="inlineStr">
         <is>
           <t>화상·메테오 연소·불장판 지속 피해 증가</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="22" customHeight="1" s="13">
-      <c r="A71" s="28" t="inlineStr">
+    <row r="72" ht="22" customHeight="1" s="13">
+      <c r="A72" s="28" t="inlineStr">
         <is>
           <t>소환수%(spiritPct)</t>
         </is>
       </c>
-      <c r="B71" s="29" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>spiritPct</t>
         </is>
       </c>
-      <c r="C71" s="30" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>% (예: 40 = +40%)</t>
         </is>
       </c>
-      <c r="D71" s="30" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>화염 정령·불사조 피해 증가</t>
         </is>
@@ -3927,8 +4017,8 @@
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A36:D36"/>

--- a/src/data/roguelike-cards.xlsx
+++ b/src/data/roguelike-cards.xlsx
@@ -1765,7 +1765,7 @@
       </c>
       <c r="G14" s="19" t="inlineStr">
         <is>
-          <t>화염구 &lt;b&gt;치명타로 마무리&lt;/b&gt;하면, 다음 스테이지의 첫 화염구 치명타가 &lt;b&gt;8배&lt;/b&gt;로 들어갑니다. (보스는 4배)</t>
+          <t>화염구 치명타 후 &lt;b&gt;3초 안에&lt;/b&gt; 몬스터를 처치하면, 다음 스테이지 처음 &lt;b&gt;20초&lt;/b&gt; 동안 치명타 피해가 &lt;b&gt;3배&lt;/b&gt;가 됩니다. (화상 제외)</t>
         </is>
       </c>
       <c r="H14" s="19" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>Finish a monster with a &lt;b&gt;Fireball crit&lt;/b&gt;, and your first Fireball crit on the next stage deals &lt;b&gt;8×&lt;/b&gt; damage (4× on bosses).</t>
+          <t>Defeat a monster within &lt;b&gt;3s&lt;/b&gt; of a Fireball crit, and for the first &lt;b&gt;20s&lt;/b&gt; of the next stage your crits deal &lt;b&gt;3×&lt;/b&gt; damage (excluding Ignite).</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="S14" s="19" t="inlineStr">
         <is>
-          <t>{"mult": 8, "bossMult": 4}</t>
+          <t>{"window": 3, "duration": 20, "critBonus": 2, "bossCritBonus": 2, "skipBossPriority": true, "keepsGuarantee": true}</t>
         </is>
       </c>
       <c r="T14" s="19" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>화염구 치명타로 몬스터를 처치하면, 다음 스테이지의 첫 화염구 치명타가 mult배(보스는 bossMult배)로 들어갑니다.</t>
+          <t>화염구 치명타 후 window초 안에 몬스터를 처치하면, 다음 스테이지 처음 duration초 동안 직격 치명타 피해가 (1+critBonus)배(보스는 1+bossCritBonus)가 됩니다. skipBossPriority: 보스 보상의 주력 빌드 전설 우선 대상에서 제외, keepsGuarantee: 보유해도 보스 전설 보장이 끝나지 않음.</t>
         </is>
       </c>
       <c r="D60" s="30" t="inlineStr">
         <is>
-          <t>{"mult": 8, "bossMult": 4}</t>
+          <t>{"window": 3, "duration": 20, "critBonus": 2, "bossCritBonus": 2, "skipBossPriority": true, "keepsGuarantee": true}</t>
         </is>
       </c>
     </row>
